--- a/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-hydrogen-electrolysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DA8584-26F2-3746-B770-CFAAEEB4980A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E81E569-BFB6-8249-8A7C-E3FA963CF6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1803,9 +1803,6 @@
     <t>chlorine, liquid</t>
   </si>
   <si>
-    <t>market for acrylic dispersion, with water, in 58% solution state</t>
-  </si>
-  <si>
     <t>acrylic dispersion, with water, in 58% solution state</t>
   </si>
   <si>
@@ -1859,6 +1856,9 @@
   </si>
   <si>
     <t>Chloride</t>
+  </si>
+  <si>
+    <t>market for acrylic dispersion, with water, in 58% solution</t>
   </si>
 </sst>
 </file>
@@ -2126,7 +2126,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -2211,22 +2211,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2241,9 +2229,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
@@ -2529,7 +2526,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U589"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:U597"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.1640625" customWidth="1"/>
@@ -2540,8 +2538,8 @@
     <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" style="60" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="60" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
     <col min="19" max="20" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2559,10 +2557,9 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="5"/>
-      <c r="J1"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="6"/>
       <c r="C2" s="2"/>
@@ -2572,10 +2569,9 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="5"/>
-      <c r="J2"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2590,7 +2586,7 @@
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
     </row>
-    <row r="4" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
@@ -2604,7 +2600,7 @@
       <c r="O4" s="12"/>
       <c r="P4" s="12"/>
     </row>
-    <row r="5" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
@@ -2618,7 +2614,7 @@
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
     </row>
-    <row r="6" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
@@ -2632,7 +2628,7 @@
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
     </row>
-    <row r="7" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>2</v>
       </c>
@@ -2646,7 +2642,7 @@
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
@@ -2663,7 +2659,7 @@
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
     </row>
-    <row r="9" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
@@ -2683,7 +2679,7 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>8</v>
       </c>
@@ -2748,7 +2744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
         <v>438</v>
       </c>
@@ -2782,7 +2778,7 @@
       <c r="P11" s="12"/>
       <c r="T11"/>
     </row>
-    <row r="12" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="str">
         <f>B123</f>
         <v>electrolyzer production, 1MWe, PEM, Stack</v>
@@ -2830,7 +2826,7 @@
         <v>1.7998560115190784E-6</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="str">
         <f>B162</f>
         <v>electrolyzer production, 1MWe, PEM, Balance of Plant</v>
@@ -2878,7 +2874,7 @@
         <v>4.4996400287976961E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>505</v>
       </c>
@@ -2928,7 +2924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>507</v>
       </c>
@@ -2978,7 +2974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>33</v>
       </c>
@@ -3023,7 +3019,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>517</v>
       </c>
@@ -3058,7 +3054,7 @@
       <c r="Q17"/>
       <c r="R17"/>
     </row>
-    <row r="18" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
         <v>38</v>
       </c>
@@ -3090,7 +3086,7 @@
       <c r="Q18" s="19"/>
       <c r="R18"/>
     </row>
-    <row r="19" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="47" t="s">
         <v>456</v>
       </c>
@@ -3154,7 +3150,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="47" t="s">
         <v>458</v>
       </c>
@@ -3208,7 +3204,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="47" t="s">
         <v>461</v>
       </c>
@@ -3262,7 +3258,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
@@ -3270,7 +3266,7 @@
       <c r="O22" s="12"/>
       <c r="P22" s="12"/>
     </row>
-    <row r="23" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>1</v>
       </c>
@@ -3285,7 +3281,7 @@
       <c r="O23" s="12"/>
       <c r="P23" s="12"/>
     </row>
-    <row r="24" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>3</v>
       </c>
@@ -3299,7 +3295,7 @@
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
     </row>
-    <row r="25" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>11</v>
       </c>
@@ -3313,7 +3309,7 @@
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
     </row>
-    <row r="26" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
         <v>4</v>
       </c>
@@ -3327,7 +3323,7 @@
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
     </row>
-    <row r="27" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>2</v>
       </c>
@@ -3341,7 +3337,7 @@
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
-    <row r="28" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>6</v>
       </c>
@@ -3358,7 +3354,7 @@
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
     </row>
-    <row r="29" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
         <v>7</v>
       </c>
@@ -3378,7 +3374,7 @@
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
     </row>
-    <row r="30" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>8</v>
       </c>
@@ -3443,7 +3439,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="str">
         <f>B23</f>
         <v>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar photovoltaic electricity</v>
@@ -3478,7 +3474,7 @@
       <c r="P31" s="12"/>
       <c r="T31"/>
     </row>
-    <row r="32" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
         <v>55</v>
       </c>
@@ -3525,7 +3521,7 @@
         <v>1.7998560115190784E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>80</v>
       </c>
@@ -3572,7 +3568,7 @@
         <v>4.4996400287976961E-7</v>
       </c>
     </row>
-    <row r="34" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>505</v>
       </c>
@@ -3622,7 +3618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>507</v>
       </c>
@@ -3672,7 +3668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="13" t="s">
         <v>490</v>
       </c>
@@ -3717,7 +3713,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="37" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="13" t="s">
         <v>517</v>
       </c>
@@ -3752,7 +3748,7 @@
       <c r="Q37"/>
       <c r="R37"/>
     </row>
-    <row r="38" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="21" t="s">
         <v>38</v>
       </c>
@@ -3784,7 +3780,7 @@
       <c r="Q38" s="19"/>
       <c r="R38"/>
     </row>
-    <row r="39" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="47" t="s">
         <v>456</v>
       </c>
@@ -3848,7 +3844,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="40" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="47" t="s">
         <v>458</v>
       </c>
@@ -3902,7 +3898,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="41" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="47" t="s">
         <v>461</v>
       </c>
@@ -3956,7 +3952,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="42" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="K42" s="12"/>
       <c r="L42" s="12"/>
       <c r="M42" s="12"/>
@@ -3964,7 +3960,7 @@
       <c r="O42" s="12"/>
       <c r="P42" s="12"/>
     </row>
-    <row r="43" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>1</v>
       </c>
@@ -3979,7 +3975,7 @@
       <c r="O43" s="12"/>
       <c r="P43" s="12"/>
     </row>
-    <row r="44" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="13" t="s">
         <v>3</v>
       </c>
@@ -3993,7 +3989,7 @@
       <c r="O44" s="12"/>
       <c r="P44" s="12"/>
     </row>
-    <row r="45" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>11</v>
       </c>
@@ -4007,7 +4003,7 @@
       <c r="O45" s="12"/>
       <c r="P45" s="12"/>
     </row>
-    <row r="46" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>4</v>
       </c>
@@ -4021,7 +4017,7 @@
       <c r="O46" s="12"/>
       <c r="P46" s="12"/>
     </row>
-    <row r="47" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
         <v>2</v>
       </c>
@@ -4035,7 +4031,7 @@
       <c r="O47" s="12"/>
       <c r="P47" s="12"/>
     </row>
-    <row r="48" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="13" t="s">
         <v>6</v>
       </c>
@@ -4052,7 +4048,7 @@
       <c r="O48" s="12"/>
       <c r="P48" s="12"/>
     </row>
-    <row r="49" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="17" t="s">
         <v>7</v>
       </c>
@@ -4072,7 +4068,7 @@
       <c r="O49" s="12"/>
       <c r="P49" s="12"/>
     </row>
-    <row r="50" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="17" t="s">
         <v>8</v>
       </c>
@@ -4137,7 +4133,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16" t="str">
         <f>B43</f>
         <v>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</v>
@@ -4172,7 +4168,7 @@
       <c r="P51" s="12"/>
       <c r="T51"/>
     </row>
-    <row r="52" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="16" t="s">
         <v>55</v>
       </c>
@@ -4219,7 +4215,7 @@
         <v>1.7998560115190784E-6</v>
       </c>
     </row>
-    <row r="53" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="16" t="s">
         <v>80</v>
       </c>
@@ -4266,7 +4262,7 @@
         <v>4.4996400287976961E-7</v>
       </c>
     </row>
-    <row r="54" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="16" t="s">
         <v>505</v>
       </c>
@@ -4316,7 +4312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="16" t="s">
         <v>507</v>
       </c>
@@ -4366,7 +4362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
         <v>493</v>
       </c>
@@ -4411,7 +4407,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="57" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="13" t="s">
         <v>517</v>
       </c>
@@ -4446,7 +4442,7 @@
       <c r="Q57"/>
       <c r="R57"/>
     </row>
-    <row r="58" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="21" t="s">
         <v>38</v>
       </c>
@@ -4478,7 +4474,7 @@
       <c r="Q58" s="19"/>
       <c r="R58"/>
     </row>
-    <row r="59" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="47" t="s">
         <v>456</v>
       </c>
@@ -4542,7 +4538,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="60" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="47" t="s">
         <v>458</v>
       </c>
@@ -4596,7 +4592,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="61" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="47" t="s">
         <v>461</v>
       </c>
@@ -4650,7 +4646,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="62" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="K62" s="12"/>
       <c r="L62" s="12"/>
       <c r="M62" s="12"/>
@@ -4658,7 +4654,7 @@
       <c r="O62" s="12"/>
       <c r="P62" s="12"/>
     </row>
-    <row r="63" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
         <v>1</v>
       </c>
@@ -4673,7 +4669,7 @@
       <c r="O63" s="12"/>
       <c r="P63" s="12"/>
     </row>
-    <row r="64" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
         <v>3</v>
       </c>
@@ -4687,7 +4683,7 @@
       <c r="O64" s="12"/>
       <c r="P64" s="12"/>
     </row>
-    <row r="65" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="13" t="s">
         <v>11</v>
       </c>
@@ -4701,7 +4697,7 @@
       <c r="O65" s="12"/>
       <c r="P65" s="12"/>
     </row>
-    <row r="66" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
         <v>4</v>
       </c>
@@ -4715,7 +4711,7 @@
       <c r="O66" s="12"/>
       <c r="P66" s="12"/>
     </row>
-    <row r="67" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
         <v>2</v>
       </c>
@@ -4729,7 +4725,7 @@
       <c r="O67" s="12"/>
       <c r="P67" s="12"/>
     </row>
-    <row r="68" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
         <v>6</v>
       </c>
@@ -4746,7 +4742,7 @@
       <c r="O68" s="12"/>
       <c r="P68" s="12"/>
     </row>
-    <row r="69" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
         <v>7</v>
       </c>
@@ -4766,7 +4762,7 @@
       <c r="O69" s="12"/>
       <c r="P69" s="12"/>
     </row>
-    <row r="70" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="17" t="s">
         <v>8</v>
       </c>
@@ -4831,7 +4827,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="str">
         <f>B63</f>
         <v>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from offshore wind electricity</v>
@@ -4866,7 +4862,7 @@
       <c r="P71" s="12"/>
       <c r="T71"/>
     </row>
-    <row r="72" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16" t="s">
         <v>55</v>
       </c>
@@ -4913,7 +4909,7 @@
         <v>1.7998560115190784E-6</v>
       </c>
     </row>
-    <row r="73" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
         <v>80</v>
       </c>
@@ -4960,7 +4956,7 @@
         <v>4.4996400287976961E-7</v>
       </c>
     </row>
-    <row r="74" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16" t="s">
         <v>505</v>
       </c>
@@ -5010,7 +5006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16" t="s">
         <v>507</v>
       </c>
@@ -5060,7 +5056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="13" t="s">
         <v>499</v>
       </c>
@@ -5105,7 +5101,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="77" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="13" t="s">
         <v>517</v>
       </c>
@@ -5140,7 +5136,7 @@
       <c r="Q77"/>
       <c r="R77"/>
     </row>
-    <row r="78" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
         <v>38</v>
       </c>
@@ -5172,7 +5168,7 @@
       <c r="Q78" s="19"/>
       <c r="R78"/>
     </row>
-    <row r="79" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="47" t="s">
         <v>456</v>
       </c>
@@ -5236,7 +5232,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="80" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="47" t="s">
         <v>458</v>
       </c>
@@ -5290,7 +5286,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="81" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="47" t="s">
         <v>461</v>
       </c>
@@ -5344,7 +5340,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="82" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="K82" s="12"/>
       <c r="L82" s="12"/>
       <c r="M82" s="12"/>
@@ -5352,7 +5348,7 @@
       <c r="O82" s="12"/>
       <c r="P82" s="12"/>
     </row>
-    <row r="83" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>1</v>
       </c>
@@ -5367,7 +5363,7 @@
       <c r="O83" s="12"/>
       <c r="P83" s="12"/>
     </row>
-    <row r="84" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="13" t="s">
         <v>3</v>
       </c>
@@ -5381,7 +5377,7 @@
       <c r="O84" s="12"/>
       <c r="P84" s="12"/>
     </row>
-    <row r="85" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="13" t="s">
         <v>11</v>
       </c>
@@ -5395,7 +5391,7 @@
       <c r="O85" s="12"/>
       <c r="P85" s="12"/>
     </row>
-    <row r="86" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="13" t="s">
         <v>4</v>
       </c>
@@ -5409,7 +5405,7 @@
       <c r="O86" s="12"/>
       <c r="P86" s="12"/>
     </row>
-    <row r="87" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="13" t="s">
         <v>2</v>
       </c>
@@ -5423,7 +5419,7 @@
       <c r="O87" s="12"/>
       <c r="P87" s="12"/>
     </row>
-    <row r="88" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="13" t="s">
         <v>6</v>
       </c>
@@ -5440,7 +5436,7 @@
       <c r="O88" s="12"/>
       <c r="P88" s="12"/>
     </row>
-    <row r="89" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="17" t="s">
         <v>7</v>
       </c>
@@ -5460,7 +5456,7 @@
       <c r="O89" s="12"/>
       <c r="P89" s="12"/>
     </row>
-    <row r="90" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="17" t="s">
         <v>8</v>
       </c>
@@ -5525,7 +5521,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="16" t="str">
         <f>B83</f>
         <v>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from geothermal electricity</v>
@@ -5560,7 +5556,7 @@
       <c r="P91" s="12"/>
       <c r="T91"/>
     </row>
-    <row r="92" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="16" t="s">
         <v>55</v>
       </c>
@@ -5607,7 +5603,7 @@
         <v>1.7998560115190784E-6</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="16" t="s">
         <v>80</v>
       </c>
@@ -5654,7 +5650,7 @@
         <v>4.4996400287976961E-7</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="16" t="s">
         <v>505</v>
       </c>
@@ -5704,7 +5700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="16" t="s">
         <v>507</v>
       </c>
@@ -5754,7 +5750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="13" t="s">
         <v>502</v>
       </c>
@@ -5799,7 +5795,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="97" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="13" t="s">
         <v>517</v>
       </c>
@@ -5834,7 +5830,7 @@
       <c r="Q97"/>
       <c r="R97"/>
     </row>
-    <row r="98" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="21" t="s">
         <v>38</v>
       </c>
@@ -5866,7 +5862,7 @@
       <c r="Q98" s="19"/>
       <c r="R98"/>
     </row>
-    <row r="99" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="47" t="s">
         <v>456</v>
       </c>
@@ -5930,7 +5926,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="100" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="47" t="s">
         <v>458</v>
       </c>
@@ -5984,7 +5980,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="101" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="47" t="s">
         <v>461</v>
       </c>
@@ -6038,7 +6034,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="102" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="K102" s="12"/>
       <c r="L102" s="12"/>
       <c r="M102" s="12"/>
@@ -6046,7 +6042,7 @@
       <c r="O102" s="12"/>
       <c r="P102" s="12"/>
     </row>
-    <row r="103" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>1</v>
       </c>
@@ -6061,7 +6057,7 @@
       <c r="O103" s="12"/>
       <c r="P103" s="12"/>
     </row>
-    <row r="104" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="13" t="s">
         <v>3</v>
       </c>
@@ -6075,7 +6071,7 @@
       <c r="O104" s="12"/>
       <c r="P104" s="12"/>
     </row>
-    <row r="105" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="13" t="s">
         <v>11</v>
       </c>
@@ -6089,7 +6085,7 @@
       <c r="O105" s="12"/>
       <c r="P105" s="12"/>
     </row>
-    <row r="106" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="13" t="s">
         <v>4</v>
       </c>
@@ -6103,7 +6099,7 @@
       <c r="O106" s="12"/>
       <c r="P106" s="12"/>
     </row>
-    <row r="107" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="13" t="s">
         <v>2</v>
       </c>
@@ -6117,7 +6113,7 @@
       <c r="O107" s="12"/>
       <c r="P107" s="12"/>
     </row>
-    <row r="108" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="13" t="s">
         <v>6</v>
       </c>
@@ -6134,7 +6130,7 @@
       <c r="O108" s="12"/>
       <c r="P108" s="12"/>
     </row>
-    <row r="109" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="17" t="s">
         <v>7</v>
       </c>
@@ -6154,7 +6150,7 @@
       <c r="O109" s="12"/>
       <c r="P109" s="12"/>
     </row>
-    <row r="110" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="17" t="s">
         <v>8</v>
       </c>
@@ -6219,7 +6215,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="111" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="16" t="str">
         <f>B103</f>
         <v>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from concentrated solar electricity</v>
@@ -6254,7 +6250,7 @@
       <c r="P111" s="12"/>
       <c r="T111"/>
     </row>
-    <row r="112" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="16" t="s">
         <v>55</v>
       </c>
@@ -6301,7 +6297,7 @@
         <v>1.7998560115190784E-6</v>
       </c>
     </row>
-    <row r="113" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="16" t="s">
         <v>80</v>
       </c>
@@ -6348,7 +6344,7 @@
         <v>4.4996400287976961E-7</v>
       </c>
     </row>
-    <row r="114" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="16" t="s">
         <v>505</v>
       </c>
@@ -6398,7 +6394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="16" t="s">
         <v>507</v>
       </c>
@@ -6448,7 +6444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="13" t="s">
         <v>504</v>
       </c>
@@ -6493,7 +6489,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="117" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="13" t="s">
         <v>517</v>
       </c>
@@ -6528,7 +6524,7 @@
       <c r="Q117"/>
       <c r="R117"/>
     </row>
-    <row r="118" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
         <v>38</v>
       </c>
@@ -6560,7 +6556,7 @@
       <c r="Q118" s="19"/>
       <c r="R118"/>
     </row>
-    <row r="119" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="47" t="s">
         <v>456</v>
       </c>
@@ -6624,7 +6620,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="120" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="47" t="s">
         <v>458</v>
       </c>
@@ -6678,7 +6674,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="121" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="47" t="s">
         <v>461</v>
       </c>
@@ -6732,7 +6728,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="122" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="K122" s="12"/>
       <c r="L122" s="12"/>
       <c r="M122" s="12"/>
@@ -6740,7 +6736,7 @@
       <c r="O122" s="12"/>
       <c r="P122" s="12"/>
     </row>
-    <row r="123" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>1</v>
       </c>
@@ -6754,7 +6750,7 @@
       <c r="O123" s="12"/>
       <c r="P123" s="12"/>
     </row>
-    <row r="124" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="13" t="s">
         <v>3</v>
       </c>
@@ -6768,7 +6764,7 @@
       <c r="O124" s="12"/>
       <c r="P124" s="12"/>
     </row>
-    <row r="125" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="13" t="s">
         <v>11</v>
       </c>
@@ -6782,7 +6778,7 @@
       <c r="O125" s="12"/>
       <c r="P125" s="12"/>
     </row>
-    <row r="126" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="13" t="s">
         <v>4</v>
       </c>
@@ -6796,7 +6792,7 @@
       <c r="O126" s="12"/>
       <c r="P126" s="12"/>
     </row>
-    <row r="127" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="13" t="s">
         <v>2</v>
       </c>
@@ -6810,7 +6806,7 @@
       <c r="O127" s="12"/>
       <c r="P127" s="12"/>
     </row>
-    <row r="128" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="13" t="s">
         <v>6</v>
       </c>
@@ -6828,7 +6824,7 @@
       <c r="O128" s="12"/>
       <c r="P128" s="12"/>
     </row>
-    <row r="129" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="17" t="s">
         <v>7</v>
       </c>
@@ -6848,7 +6844,7 @@
       <c r="O129" s="12"/>
       <c r="P129" s="12"/>
     </row>
-    <row r="130" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="17" t="s">
         <v>8</v>
       </c>
@@ -6894,7 +6890,7 @@
       <c r="S130" s="17"/>
       <c r="T130" s="7"/>
     </row>
-    <row r="131" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="16" t="str">
         <f>B123</f>
         <v>electrolyzer production, 1MWe, PEM, Stack</v>
@@ -6926,7 +6922,7 @@
       <c r="O131" s="12"/>
       <c r="P131" s="12"/>
     </row>
-    <row r="132" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="11" t="s">
         <v>18</v>
       </c>
@@ -6961,7 +6957,7 @@
       <c r="Q132"/>
       <c r="R132"/>
     </row>
-    <row r="133" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="11" t="s">
         <v>58</v>
       </c>
@@ -6996,7 +6992,7 @@
       <c r="Q133"/>
       <c r="R133"/>
     </row>
-    <row r="134" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="11" t="s">
         <v>59</v>
       </c>
@@ -7031,7 +7027,7 @@
       <c r="Q134"/>
       <c r="R134"/>
     </row>
-    <row r="135" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="11" t="s">
         <v>21</v>
       </c>
@@ -7066,7 +7062,7 @@
       <c r="Q135"/>
       <c r="R135"/>
     </row>
-    <row r="136" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="11" t="s">
         <v>63</v>
       </c>
@@ -7101,7 +7097,7 @@
       <c r="Q136"/>
       <c r="R136"/>
     </row>
-    <row r="137" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="11" t="s">
         <v>479</v>
       </c>
@@ -7136,7 +7132,7 @@
       <c r="Q137"/>
       <c r="R137"/>
     </row>
-    <row r="138" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="11" t="s">
         <v>23</v>
       </c>
@@ -7180,7 +7176,7 @@
       <c r="Q138"/>
       <c r="R138"/>
     </row>
-    <row r="139" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="11" t="s">
         <v>63</v>
       </c>
@@ -7215,7 +7211,7 @@
       <c r="Q139"/>
       <c r="R139"/>
     </row>
-    <row r="140" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="11" t="s">
         <v>68</v>
       </c>
@@ -7250,7 +7246,7 @@
       <c r="Q140"/>
       <c r="R140"/>
     </row>
-    <row r="141" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="11" t="s">
         <v>71</v>
       </c>
@@ -7285,7 +7281,7 @@
       <c r="Q141"/>
       <c r="R141"/>
     </row>
-    <row r="142" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="11" t="s">
         <v>73</v>
       </c>
@@ -7320,7 +7316,7 @@
       <c r="Q142"/>
       <c r="R142"/>
     </row>
-    <row r="143" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="11" t="s">
         <v>20</v>
       </c>
@@ -7355,7 +7351,7 @@
       <c r="Q143"/>
       <c r="R143"/>
     </row>
-    <row r="144" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="11" t="s">
         <v>76</v>
       </c>
@@ -7390,7 +7386,7 @@
       <c r="Q144"/>
       <c r="R144"/>
     </row>
-    <row r="145" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="11" t="s">
         <v>33</v>
       </c>
@@ -7426,7 +7422,7 @@
       <c r="Q145"/>
       <c r="R145"/>
     </row>
-    <row r="146" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B146" s="16"/>
       <c r="K146" s="12"/>
       <c r="L146" s="12"/>
@@ -7435,7 +7431,7 @@
       <c r="O146" s="12"/>
       <c r="P146" s="12"/>
     </row>
-    <row r="147" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>1</v>
       </c>
@@ -7449,7 +7445,7 @@
       <c r="O147" s="12"/>
       <c r="P147" s="12"/>
     </row>
-    <row r="148" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="13" t="s">
         <v>3</v>
       </c>
@@ -7463,7 +7459,7 @@
       <c r="O148" s="12"/>
       <c r="P148" s="12"/>
     </row>
-    <row r="149" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="13" t="s">
         <v>11</v>
       </c>
@@ -7477,7 +7473,7 @@
       <c r="O149" s="12"/>
       <c r="P149" s="12"/>
     </row>
-    <row r="150" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="13" t="s">
         <v>4</v>
       </c>
@@ -7491,7 +7487,7 @@
       <c r="O150" s="12"/>
       <c r="P150" s="12"/>
     </row>
-    <row r="151" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="13" t="s">
         <v>2</v>
       </c>
@@ -7505,7 +7501,7 @@
       <c r="O151" s="12"/>
       <c r="P151" s="12"/>
     </row>
-    <row r="152" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="13" t="s">
         <v>6</v>
       </c>
@@ -7519,7 +7515,7 @@
       <c r="O152" s="12"/>
       <c r="P152" s="12"/>
     </row>
-    <row r="153" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="17" t="s">
         <v>7</v>
       </c>
@@ -7539,7 +7535,7 @@
       <c r="O153" s="12"/>
       <c r="P153" s="12"/>
     </row>
-    <row r="154" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="17" t="s">
         <v>8</v>
       </c>
@@ -7577,7 +7573,7 @@
       <c r="S154" s="17"/>
       <c r="T154" s="7"/>
     </row>
-    <row r="155" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="16" t="str">
         <f>B147</f>
         <v>treatment of electrolyzer stack, 1MWe, PEM</v>
@@ -7606,7 +7602,7 @@
       <c r="O155" s="12"/>
       <c r="P155" s="12"/>
     </row>
-    <row r="156" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="16" t="s">
         <v>204</v>
       </c>
@@ -7636,7 +7632,7 @@
       <c r="Q156"/>
       <c r="R156"/>
     </row>
-    <row r="157" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="11" t="s">
         <v>206</v>
       </c>
@@ -7666,7 +7662,7 @@
       <c r="Q157"/>
       <c r="R157"/>
     </row>
-    <row r="158" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="11" t="s">
         <v>208</v>
       </c>
@@ -7696,7 +7692,7 @@
       <c r="Q158"/>
       <c r="R158"/>
     </row>
-    <row r="159" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="11" t="s">
         <v>210</v>
       </c>
@@ -7726,7 +7722,7 @@
       <c r="Q159"/>
       <c r="R159"/>
     </row>
-    <row r="160" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="11" t="s">
         <v>213</v>
       </c>
@@ -7756,7 +7752,7 @@
       <c r="Q160"/>
       <c r="R160"/>
     </row>
-    <row r="161" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B161" s="16"/>
       <c r="K161" s="12"/>
       <c r="L161" s="12"/>
@@ -7765,7 +7761,7 @@
       <c r="O161" s="12"/>
       <c r="P161" s="12"/>
     </row>
-    <row r="162" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>1</v>
       </c>
@@ -7779,7 +7775,7 @@
       <c r="O162" s="12"/>
       <c r="P162" s="12"/>
     </row>
-    <row r="163" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="13" t="s">
         <v>3</v>
       </c>
@@ -7793,7 +7789,7 @@
       <c r="O163" s="12"/>
       <c r="P163" s="12"/>
     </row>
-    <row r="164" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="13" t="s">
         <v>11</v>
       </c>
@@ -7807,7 +7803,7 @@
       <c r="O164" s="12"/>
       <c r="P164" s="12"/>
     </row>
-    <row r="165" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="13" t="s">
         <v>4</v>
       </c>
@@ -7821,7 +7817,7 @@
       <c r="O165" s="12"/>
       <c r="P165" s="12"/>
     </row>
-    <row r="166" spans="1:20" s="11" customFormat="1" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:20" s="11" customFormat="1" ht="16.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="13" t="s">
         <v>2</v>
       </c>
@@ -7835,7 +7831,7 @@
       <c r="O166" s="12"/>
       <c r="P166" s="12"/>
     </row>
-    <row r="167" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="13" t="s">
         <v>6</v>
       </c>
@@ -7851,7 +7847,7 @@
       <c r="O167" s="12"/>
       <c r="P167" s="12"/>
     </row>
-    <row r="168" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="17" t="s">
         <v>7</v>
       </c>
@@ -7870,7 +7866,7 @@
       <c r="O168" s="12"/>
       <c r="P168" s="12"/>
     </row>
-    <row r="169" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="17" t="s">
         <v>8</v>
       </c>
@@ -7908,7 +7904,7 @@
       <c r="S169" s="17"/>
       <c r="T169" s="7"/>
     </row>
-    <row r="170" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="16" t="str">
         <f>B162</f>
         <v>electrolyzer production, 1MWe, PEM, Balance of Plant</v>
@@ -7938,7 +7934,7 @@
       <c r="O170" s="12"/>
       <c r="P170" s="26"/>
     </row>
-    <row r="171" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="11" t="s">
         <v>18</v>
       </c>
@@ -7970,7 +7966,7 @@
       <c r="Q171"/>
       <c r="R171"/>
     </row>
-    <row r="172" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="11" t="s">
         <v>68</v>
       </c>
@@ -8002,7 +7998,7 @@
       <c r="Q172"/>
       <c r="R172"/>
     </row>
-    <row r="173" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="11" t="s">
         <v>83</v>
       </c>
@@ -8034,7 +8030,7 @@
       <c r="Q173"/>
       <c r="R173"/>
     </row>
-    <row r="174" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="11" t="s">
         <v>58</v>
       </c>
@@ -8066,7 +8062,7 @@
       <c r="Q174"/>
       <c r="R174"/>
     </row>
-    <row r="175" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="11" t="s">
         <v>84</v>
       </c>
@@ -8098,7 +8094,7 @@
       <c r="Q175"/>
       <c r="R175"/>
     </row>
-    <row r="176" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="11" t="s">
         <v>85</v>
       </c>
@@ -8130,7 +8126,7 @@
       <c r="Q176"/>
       <c r="R176"/>
     </row>
-    <row r="177" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="11" t="s">
         <v>86</v>
       </c>
@@ -8162,7 +8158,7 @@
       <c r="Q177"/>
       <c r="R177"/>
     </row>
-    <row r="178" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="11" t="s">
         <v>30</v>
       </c>
@@ -8194,7 +8190,7 @@
       <c r="Q178"/>
       <c r="R178"/>
     </row>
-    <row r="179" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="11" t="s">
         <v>25</v>
       </c>
@@ -8226,7 +8222,7 @@
       <c r="Q179"/>
       <c r="R179"/>
     </row>
-    <row r="180" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="11" t="s">
         <v>84</v>
       </c>
@@ -8258,7 +8254,7 @@
       <c r="Q180"/>
       <c r="R180"/>
     </row>
-    <row r="181" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="11" t="s">
         <v>73</v>
       </c>
@@ -8290,7 +8286,7 @@
       <c r="Q181"/>
       <c r="R181"/>
     </row>
-    <row r="182" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="11" t="s">
         <v>20</v>
       </c>
@@ -8322,7 +8318,7 @@
       <c r="Q182"/>
       <c r="R182"/>
     </row>
-    <row r="183" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
         <v>18</v>
       </c>
@@ -8354,7 +8350,7 @@
       <c r="Q183"/>
       <c r="R183"/>
     </row>
-    <row r="184" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="11" t="s">
         <v>58</v>
       </c>
@@ -8386,7 +8382,7 @@
       <c r="Q184"/>
       <c r="R184"/>
     </row>
-    <row r="185" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="11" t="s">
         <v>68</v>
       </c>
@@ -8418,7 +8414,7 @@
       <c r="Q185"/>
       <c r="R185"/>
     </row>
-    <row r="186" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="11" t="s">
         <v>71</v>
       </c>
@@ -8450,7 +8446,7 @@
       <c r="Q186"/>
       <c r="R186"/>
     </row>
-    <row r="187" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="11" t="s">
         <v>27</v>
       </c>
@@ -8482,7 +8478,7 @@
       <c r="Q187"/>
       <c r="R187"/>
     </row>
-    <row r="188" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="11" t="s">
         <v>93</v>
       </c>
@@ -8514,7 +8510,7 @@
       <c r="Q188"/>
       <c r="R188"/>
     </row>
-    <row r="189" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="11" t="s">
         <v>95</v>
       </c>
@@ -8546,7 +8542,7 @@
       <c r="Q189"/>
       <c r="R189"/>
     </row>
-    <row r="190" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
         <v>98</v>
       </c>
@@ -8578,7 +8574,7 @@
       <c r="Q190"/>
       <c r="R190"/>
     </row>
-    <row r="191" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="11" t="s">
         <v>73</v>
       </c>
@@ -8610,7 +8606,7 @@
       <c r="Q191"/>
       <c r="R191"/>
     </row>
-    <row r="192" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="11" t="s">
         <v>20</v>
       </c>
@@ -8642,7 +8638,7 @@
       <c r="Q192"/>
       <c r="R192"/>
     </row>
-    <row r="193" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="11" t="s">
         <v>102</v>
       </c>
@@ -8674,7 +8670,7 @@
       <c r="Q193"/>
       <c r="R193"/>
     </row>
-    <row r="194" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="11" t="s">
         <v>105</v>
       </c>
@@ -8706,7 +8702,7 @@
       <c r="Q194"/>
       <c r="R194"/>
     </row>
-    <row r="195" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="11" t="s">
         <v>83</v>
       </c>
@@ -8738,7 +8734,7 @@
       <c r="Q195"/>
       <c r="R195"/>
     </row>
-    <row r="196" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="11" t="s">
         <v>84</v>
       </c>
@@ -8770,7 +8766,7 @@
       <c r="Q196"/>
       <c r="R196"/>
     </row>
-    <row r="197" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="11" t="s">
         <v>18</v>
       </c>
@@ -8802,7 +8798,7 @@
       <c r="Q197"/>
       <c r="R197"/>
     </row>
-    <row r="198" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="11" t="s">
         <v>68</v>
       </c>
@@ -8834,7 +8830,7 @@
       <c r="Q198"/>
       <c r="R198"/>
     </row>
-    <row r="199" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="11" t="s">
         <v>83</v>
       </c>
@@ -8866,7 +8862,7 @@
       <c r="Q199"/>
       <c r="R199"/>
     </row>
-    <row r="200" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="11" t="s">
         <v>85</v>
       </c>
@@ -8898,7 +8894,7 @@
       <c r="Q200"/>
       <c r="R200"/>
     </row>
-    <row r="201" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="11" t="s">
         <v>86</v>
       </c>
@@ -8930,7 +8926,7 @@
       <c r="Q201"/>
       <c r="R201"/>
     </row>
-    <row r="202" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="11" t="s">
         <v>108</v>
       </c>
@@ -8962,7 +8958,7 @@
       <c r="Q202"/>
       <c r="R202"/>
     </row>
-    <row r="203" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="11" t="s">
         <v>111</v>
       </c>
@@ -8994,7 +8990,7 @@
       <c r="Q203"/>
       <c r="R203"/>
     </row>
-    <row r="204" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="11" t="s">
         <v>83</v>
       </c>
@@ -9026,7 +9022,7 @@
       <c r="Q204"/>
       <c r="R204"/>
     </row>
-    <row r="205" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="11" t="s">
         <v>73</v>
       </c>
@@ -9058,7 +9054,7 @@
       <c r="Q205"/>
       <c r="R205"/>
     </row>
-    <row r="206" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="11" t="s">
         <v>84</v>
       </c>
@@ -9090,7 +9086,7 @@
       <c r="Q206"/>
       <c r="R206"/>
     </row>
-    <row r="207" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="11" t="s">
         <v>20</v>
       </c>
@@ -9122,7 +9118,7 @@
       <c r="Q207"/>
       <c r="R207"/>
     </row>
-    <row r="208" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="11" t="s">
         <v>83</v>
       </c>
@@ -9154,7 +9150,7 @@
       <c r="Q208"/>
       <c r="R208"/>
     </row>
-    <row r="209" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="11" t="s">
         <v>73</v>
       </c>
@@ -9186,7 +9182,7 @@
       <c r="Q209"/>
       <c r="R209"/>
     </row>
-    <row r="210" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="11" t="s">
         <v>84</v>
       </c>
@@ -9218,7 +9214,7 @@
       <c r="Q210"/>
       <c r="R210"/>
     </row>
-    <row r="211" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="11" t="s">
         <v>20</v>
       </c>
@@ -9250,7 +9246,7 @@
       <c r="Q211"/>
       <c r="R211"/>
     </row>
-    <row r="212" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="11" t="s">
         <v>73</v>
       </c>
@@ -9282,7 +9278,7 @@
       <c r="Q212"/>
       <c r="R212"/>
     </row>
-    <row r="213" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="11" t="s">
         <v>20</v>
       </c>
@@ -9314,7 +9310,7 @@
       <c r="Q213"/>
       <c r="R213"/>
     </row>
-    <row r="214" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="11" t="s">
         <v>115</v>
       </c>
@@ -9346,7 +9342,7 @@
       <c r="Q214"/>
       <c r="R214"/>
     </row>
-    <row r="215" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="11" t="s">
         <v>84</v>
       </c>
@@ -9378,7 +9374,7 @@
       <c r="Q215"/>
       <c r="R215"/>
     </row>
-    <row r="216" spans="1:18" s="11" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:18" s="11" customFormat="1" ht="15.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="28" t="s">
         <v>25</v>
       </c>
@@ -9410,7 +9406,7 @@
       <c r="Q216"/>
       <c r="R216"/>
     </row>
-    <row r="217" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="11" t="s">
         <v>119</v>
       </c>
@@ -9442,7 +9438,7 @@
       <c r="Q217"/>
       <c r="R217"/>
     </row>
-    <row r="218" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="11" t="s">
         <v>33</v>
       </c>
@@ -9474,7 +9470,7 @@
       <c r="Q218"/>
       <c r="R218"/>
     </row>
-    <row r="219" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B219" s="16"/>
       <c r="K219" s="12"/>
       <c r="L219" s="12"/>
@@ -9483,7 +9479,7 @@
       <c r="O219" s="12"/>
       <c r="P219" s="12"/>
     </row>
-    <row r="220" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8" t="s">
         <v>1</v>
       </c>
@@ -9497,7 +9493,7 @@
       <c r="O220" s="12"/>
       <c r="P220" s="12"/>
     </row>
-    <row r="221" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="13" t="s">
         <v>3</v>
       </c>
@@ -9511,7 +9507,7 @@
       <c r="O221" s="12"/>
       <c r="P221" s="12"/>
     </row>
-    <row r="222" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="13" t="s">
         <v>11</v>
       </c>
@@ -9525,7 +9521,7 @@
       <c r="O222" s="12"/>
       <c r="P222" s="12"/>
     </row>
-    <row r="223" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="13" t="s">
         <v>4</v>
       </c>
@@ -9539,7 +9535,7 @@
       <c r="O223" s="12"/>
       <c r="P223" s="12"/>
     </row>
-    <row r="224" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="13" t="s">
         <v>2</v>
       </c>
@@ -9553,7 +9549,7 @@
       <c r="O224" s="12"/>
       <c r="P224" s="12"/>
     </row>
-    <row r="225" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="13" t="s">
         <v>6</v>
       </c>
@@ -9567,7 +9563,7 @@
       <c r="O225" s="12"/>
       <c r="P225" s="12"/>
     </row>
-    <row r="226" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="17" t="s">
         <v>7</v>
       </c>
@@ -9587,7 +9583,7 @@
       <c r="O226" s="12"/>
       <c r="P226" s="12"/>
     </row>
-    <row r="227" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="17" t="s">
         <v>8</v>
       </c>
@@ -9625,7 +9621,7 @@
       <c r="S227" s="17"/>
       <c r="T227" s="7"/>
     </row>
-    <row r="228" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="16" t="str">
         <f>B220</f>
         <v>treatment of electrolyzer balance of plant, 1MWe, PEM</v>
@@ -9654,7 +9650,7 @@
       <c r="O228" s="12"/>
       <c r="P228" s="12"/>
     </row>
-    <row r="229" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="16" t="s">
         <v>204</v>
       </c>
@@ -9684,7 +9680,7 @@
       <c r="Q229"/>
       <c r="R229"/>
     </row>
-    <row r="230" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="16" t="s">
         <v>449</v>
       </c>
@@ -9713,7 +9709,7 @@
       <c r="Q230"/>
       <c r="R230"/>
     </row>
-    <row r="231" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="11" t="s">
         <v>206</v>
       </c>
@@ -9742,7 +9738,7 @@
       <c r="Q231"/>
       <c r="R231"/>
     </row>
-    <row r="232" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="11" t="s">
         <v>226</v>
       </c>
@@ -9771,7 +9767,7 @@
       <c r="Q232"/>
       <c r="R232"/>
     </row>
-    <row r="233" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="11" t="s">
         <v>218</v>
       </c>
@@ -9800,7 +9796,7 @@
       <c r="Q233"/>
       <c r="R233"/>
     </row>
-    <row r="234" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="11" t="s">
         <v>219</v>
       </c>
@@ -9829,7 +9825,7 @@
       <c r="Q234"/>
       <c r="R234"/>
     </row>
-    <row r="235" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="11" t="s">
         <v>221</v>
       </c>
@@ -9858,7 +9854,7 @@
       <c r="Q235"/>
       <c r="R235"/>
     </row>
-    <row r="236" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="11" t="s">
         <v>451</v>
       </c>
@@ -9887,7 +9883,7 @@
       <c r="Q236"/>
       <c r="R236"/>
     </row>
-    <row r="237" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="11" t="s">
         <v>208</v>
       </c>
@@ -9916,7 +9912,7 @@
       <c r="Q237"/>
       <c r="R237"/>
     </row>
-    <row r="238" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="11" t="s">
         <v>210</v>
       </c>
@@ -9945,7 +9941,7 @@
       <c r="Q238"/>
       <c r="R238"/>
     </row>
-    <row r="239" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="11" t="s">
         <v>448</v>
       </c>
@@ -9974,7 +9970,7 @@
       <c r="Q239"/>
       <c r="R239"/>
     </row>
-    <row r="240" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="11" t="s">
         <v>224</v>
       </c>
@@ -10003,7 +9999,7 @@
       <c r="Q240"/>
       <c r="R240"/>
     </row>
-    <row r="241" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B241" s="16"/>
       <c r="K241" s="12"/>
       <c r="L241" s="12"/>
@@ -10012,7 +10008,7 @@
       <c r="O241" s="12"/>
       <c r="P241" s="12"/>
     </row>
-    <row r="242" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8" t="s">
         <v>1</v>
       </c>
@@ -10027,7 +10023,7 @@
       <c r="O242" s="12"/>
       <c r="P242" s="12"/>
     </row>
-    <row r="243" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="13" t="s">
         <v>3</v>
       </c>
@@ -10041,7 +10037,7 @@
       <c r="O243" s="12"/>
       <c r="P243" s="12"/>
     </row>
-    <row r="244" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="13" t="s">
         <v>11</v>
       </c>
@@ -10055,7 +10051,7 @@
       <c r="O244" s="12"/>
       <c r="P244" s="12"/>
     </row>
-    <row r="245" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="13" t="s">
         <v>4</v>
       </c>
@@ -10069,7 +10065,7 @@
       <c r="O245" s="12"/>
       <c r="P245" s="12"/>
     </row>
-    <row r="246" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="13" t="s">
         <v>2</v>
       </c>
@@ -10083,7 +10079,7 @@
       <c r="O246" s="12"/>
       <c r="P246" s="12"/>
     </row>
-    <row r="247" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="13" t="s">
         <v>6</v>
       </c>
@@ -10100,7 +10096,7 @@
       <c r="O247" s="12"/>
       <c r="P247" s="12"/>
     </row>
-    <row r="248" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="17" t="s">
         <v>7</v>
       </c>
@@ -10120,7 +10116,7 @@
       <c r="O248" s="12"/>
       <c r="P248" s="12"/>
     </row>
-    <row r="249" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="17" t="s">
         <v>8</v>
       </c>
@@ -10185,7 +10181,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="250" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="16" t="s">
         <v>439</v>
       </c>
@@ -10217,7 +10213,7 @@
       <c r="P250" s="12"/>
       <c r="T250"/>
     </row>
-    <row r="251" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="16" t="str">
         <f>B263</f>
         <v>electrolyzer production, 1MWe, AEC, Stack</v>
@@ -10265,7 +10261,7 @@
         <v>1.1478420569329661E-6</v>
       </c>
     </row>
-    <row r="252" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="16" t="str">
         <f>B292</f>
         <v>electrolyzer production, 1MWe, AEC, Balance of Plant</v>
@@ -10313,7 +10309,7 @@
         <v>2.8696051423324152E-7</v>
       </c>
     </row>
-    <row r="253" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="16" t="s">
         <v>509</v>
       </c>
@@ -10363,7 +10359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="16" t="s">
         <v>511</v>
       </c>
@@ -10413,7 +10409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="13" t="s">
         <v>50</v>
       </c>
@@ -10458,7 +10454,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="256" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="13" t="s">
         <v>125</v>
       </c>
@@ -10491,7 +10487,7 @@
       <c r="Q256"/>
       <c r="R256"/>
     </row>
-    <row r="257" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="13" t="s">
         <v>517</v>
       </c>
@@ -10523,7 +10519,7 @@
       <c r="Q257"/>
       <c r="R257"/>
     </row>
-    <row r="258" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="21" t="s">
         <v>38</v>
       </c>
@@ -10552,7 +10548,7 @@
       <c r="Q258" s="19"/>
       <c r="R258"/>
     </row>
-    <row r="259" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="47" t="s">
         <v>456</v>
       </c>
@@ -10616,7 +10612,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="260" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="47" t="s">
         <v>458</v>
       </c>
@@ -10670,7 +10666,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="261" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="47" t="s">
         <v>461</v>
       </c>
@@ -10724,7 +10720,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="262" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B262" s="16"/>
       <c r="K262" s="12"/>
       <c r="L262" s="12"/>
@@ -10733,7 +10729,7 @@
       <c r="O262" s="12"/>
       <c r="P262" s="12"/>
     </row>
-    <row r="263" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="8" t="s">
         <v>1</v>
       </c>
@@ -10747,7 +10743,7 @@
       <c r="O263" s="12"/>
       <c r="P263" s="12"/>
     </row>
-    <row r="264" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="13" t="s">
         <v>3</v>
       </c>
@@ -10761,7 +10757,7 @@
       <c r="O264" s="12"/>
       <c r="P264" s="12"/>
     </row>
-    <row r="265" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="13" t="s">
         <v>11</v>
       </c>
@@ -10775,7 +10771,7 @@
       <c r="O265" s="12"/>
       <c r="P265" s="12"/>
     </row>
-    <row r="266" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="13" t="s">
         <v>4</v>
       </c>
@@ -10789,7 +10785,7 @@
       <c r="O266" s="12"/>
       <c r="P266" s="12"/>
     </row>
-    <row r="267" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="13" t="s">
         <v>2</v>
       </c>
@@ -10803,7 +10799,7 @@
       <c r="O267" s="12"/>
       <c r="P267" s="12"/>
     </row>
-    <row r="268" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="13" t="s">
         <v>6</v>
       </c>
@@ -10817,7 +10813,7 @@
       <c r="O268" s="12"/>
       <c r="P268" s="12"/>
     </row>
-    <row r="269" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="17" t="s">
         <v>7</v>
       </c>
@@ -10837,7 +10833,7 @@
       <c r="O269" s="12"/>
       <c r="P269" s="12"/>
     </row>
-    <row r="270" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="17" t="s">
         <v>8</v>
       </c>
@@ -10875,7 +10871,7 @@
       <c r="S270" s="17"/>
       <c r="T270" s="7"/>
     </row>
-    <row r="271" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="16" t="str">
         <f>B263</f>
         <v>electrolyzer production, 1MWe, AEC, Stack</v>
@@ -10904,7 +10900,7 @@
       <c r="O271" s="12"/>
       <c r="P271" s="12"/>
     </row>
-    <row r="272" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="11" t="s">
         <v>21</v>
       </c>
@@ -10936,7 +10932,7 @@
       <c r="Q272"/>
       <c r="R272"/>
     </row>
-    <row r="273" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
         <v>73</v>
       </c>
@@ -10968,7 +10964,7 @@
       <c r="Q273"/>
       <c r="R273"/>
     </row>
-    <row r="274" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="11" t="s">
         <v>20</v>
       </c>
@@ -11000,7 +10996,7 @@
       <c r="Q274"/>
       <c r="R274"/>
     </row>
-    <row r="275" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="11" t="s">
         <v>131</v>
       </c>
@@ -11032,7 +11028,7 @@
       <c r="Q275"/>
       <c r="R275"/>
     </row>
-    <row r="276" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
         <v>133</v>
       </c>
@@ -11065,7 +11061,7 @@
       <c r="Q276"/>
       <c r="R276"/>
     </row>
-    <row r="277" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="11" t="s">
         <v>136</v>
       </c>
@@ -11098,7 +11094,7 @@
       <c r="Q277"/>
       <c r="R277"/>
     </row>
-    <row r="278" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="11" t="s">
         <v>33</v>
       </c>
@@ -11131,7 +11127,7 @@
       <c r="Q278"/>
       <c r="R278"/>
     </row>
-    <row r="279" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B279" s="16"/>
       <c r="F279" s="10"/>
       <c r="G279" s="10"/>
@@ -11142,7 +11138,7 @@
       <c r="O279" s="12"/>
       <c r="P279" s="12"/>
     </row>
-    <row r="280" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8" t="s">
         <v>1</v>
       </c>
@@ -11156,7 +11152,7 @@
       <c r="O280" s="12"/>
       <c r="P280" s="12"/>
     </row>
-    <row r="281" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="13" t="s">
         <v>3</v>
       </c>
@@ -11170,7 +11166,7 @@
       <c r="O281" s="12"/>
       <c r="P281" s="12"/>
     </row>
-    <row r="282" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="13" t="s">
         <v>11</v>
       </c>
@@ -11184,7 +11180,7 @@
       <c r="O282" s="12"/>
       <c r="P282" s="12"/>
     </row>
-    <row r="283" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="13" t="s">
         <v>4</v>
       </c>
@@ -11198,7 +11194,7 @@
       <c r="O283" s="12"/>
       <c r="P283" s="12"/>
     </row>
-    <row r="284" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="13" t="s">
         <v>2</v>
       </c>
@@ -11212,7 +11208,7 @@
       <c r="O284" s="12"/>
       <c r="P284" s="12"/>
     </row>
-    <row r="285" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="13" t="s">
         <v>6</v>
       </c>
@@ -11226,7 +11222,7 @@
       <c r="O285" s="12"/>
       <c r="P285" s="12"/>
     </row>
-    <row r="286" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="17" t="s">
         <v>7</v>
       </c>
@@ -11246,7 +11242,7 @@
       <c r="O286" s="12"/>
       <c r="P286" s="12"/>
     </row>
-    <row r="287" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="17" t="s">
         <v>8</v>
       </c>
@@ -11284,7 +11280,7 @@
       <c r="S287" s="17"/>
       <c r="T287" s="7"/>
     </row>
-    <row r="288" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="16" t="str">
         <f>B280</f>
         <v>treatment of electrolyzer stack, 1MWe, AEC</v>
@@ -11313,7 +11309,7 @@
       <c r="O288" s="12"/>
       <c r="P288" s="12"/>
     </row>
-    <row r="289" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="16" t="s">
         <v>204</v>
       </c>
@@ -11342,7 +11338,7 @@
       <c r="Q289"/>
       <c r="R289"/>
     </row>
-    <row r="290" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="11" t="s">
         <v>210</v>
       </c>
@@ -11371,7 +11367,7 @@
       <c r="Q290"/>
       <c r="R290"/>
     </row>
-    <row r="291" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B291" s="16"/>
       <c r="K291" s="12"/>
       <c r="L291" s="12"/>
@@ -11380,7 +11376,7 @@
       <c r="O291" s="12"/>
       <c r="P291" s="12"/>
     </row>
-    <row r="292" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="8" t="s">
         <v>1</v>
       </c>
@@ -11394,7 +11390,7 @@
       <c r="O292" s="12"/>
       <c r="P292" s="12"/>
     </row>
-    <row r="293" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="13" t="s">
         <v>3</v>
       </c>
@@ -11408,7 +11404,7 @@
       <c r="O293" s="12"/>
       <c r="P293" s="12"/>
     </row>
-    <row r="294" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="13" t="s">
         <v>11</v>
       </c>
@@ -11422,7 +11418,7 @@
       <c r="O294" s="12"/>
       <c r="P294" s="12"/>
     </row>
-    <row r="295" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="13" t="s">
         <v>4</v>
       </c>
@@ -11436,7 +11432,7 @@
       <c r="O295" s="12"/>
       <c r="P295" s="12"/>
     </row>
-    <row r="296" spans="1:20" s="11" customFormat="1" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:20" s="11" customFormat="1" ht="16.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="13" t="s">
         <v>2</v>
       </c>
@@ -11450,7 +11446,7 @@
       <c r="O296" s="12"/>
       <c r="P296" s="12"/>
     </row>
-    <row r="297" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="13" t="s">
         <v>6</v>
       </c>
@@ -11466,7 +11462,7 @@
       <c r="O297" s="12"/>
       <c r="P297" s="12"/>
     </row>
-    <row r="298" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="17" t="s">
         <v>7</v>
       </c>
@@ -11485,7 +11481,7 @@
       <c r="O298" s="12"/>
       <c r="P298" s="12"/>
     </row>
-    <row r="299" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="17" t="s">
         <v>8</v>
       </c>
@@ -11523,7 +11519,7 @@
       <c r="S299" s="17"/>
       <c r="T299" s="7"/>
     </row>
-    <row r="300" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="16" t="str">
         <f>B292</f>
         <v>electrolyzer production, 1MWe, AEC, Balance of Plant</v>
@@ -11554,7 +11550,7 @@
       <c r="O300" s="12"/>
       <c r="P300" s="12"/>
     </row>
-    <row r="301" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="11" t="s">
         <v>18</v>
       </c>
@@ -11586,7 +11582,7 @@
       <c r="Q301"/>
       <c r="R301"/>
     </row>
-    <row r="302" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="11" t="s">
         <v>68</v>
       </c>
@@ -11618,7 +11614,7 @@
       <c r="Q302"/>
       <c r="R302"/>
     </row>
-    <row r="303" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="11" t="s">
         <v>83</v>
       </c>
@@ -11650,7 +11646,7 @@
       <c r="Q303"/>
       <c r="R303"/>
     </row>
-    <row r="304" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="11" t="s">
         <v>58</v>
       </c>
@@ -11682,7 +11678,7 @@
       <c r="Q304"/>
       <c r="R304"/>
     </row>
-    <row r="305" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="11" t="s">
         <v>84</v>
       </c>
@@ -11714,7 +11710,7 @@
       <c r="Q305"/>
       <c r="R305"/>
     </row>
-    <row r="306" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="11" t="s">
         <v>85</v>
       </c>
@@ -11746,7 +11742,7 @@
       <c r="Q306"/>
       <c r="R306"/>
     </row>
-    <row r="307" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="11" t="s">
         <v>86</v>
       </c>
@@ -11778,7 +11774,7 @@
       <c r="Q307"/>
       <c r="R307"/>
     </row>
-    <row r="308" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="11" t="s">
         <v>30</v>
       </c>
@@ -11810,7 +11806,7 @@
       <c r="Q308"/>
       <c r="R308"/>
     </row>
-    <row r="309" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="11" t="s">
         <v>140</v>
       </c>
@@ -11842,7 +11838,7 @@
       <c r="Q309"/>
       <c r="R309"/>
     </row>
-    <row r="310" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="11" t="s">
         <v>83</v>
       </c>
@@ -11874,7 +11870,7 @@
       <c r="Q310"/>
       <c r="R310"/>
     </row>
-    <row r="311" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="11" t="s">
         <v>84</v>
       </c>
@@ -11906,7 +11902,7 @@
       <c r="Q311"/>
       <c r="R311"/>
     </row>
-    <row r="312" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="11" t="s">
         <v>73</v>
       </c>
@@ -11938,7 +11934,7 @@
       <c r="Q312"/>
       <c r="R312"/>
     </row>
-    <row r="313" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="11" t="s">
         <v>20</v>
       </c>
@@ -11970,7 +11966,7 @@
       <c r="Q313"/>
       <c r="R313"/>
     </row>
-    <row r="314" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="11" t="s">
         <v>103</v>
       </c>
@@ -12002,7 +11998,7 @@
       <c r="Q314"/>
       <c r="R314"/>
     </row>
-    <row r="315" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="11" t="s">
         <v>105</v>
       </c>
@@ -12034,7 +12030,7 @@
       <c r="Q315"/>
       <c r="R315"/>
     </row>
-    <row r="316" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="11" t="s">
         <v>83</v>
       </c>
@@ -12066,7 +12062,7 @@
       <c r="Q316"/>
       <c r="R316"/>
     </row>
-    <row r="317" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="11" t="s">
         <v>84</v>
       </c>
@@ -12098,7 +12094,7 @@
       <c r="Q317"/>
       <c r="R317"/>
     </row>
-    <row r="318" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="11" t="s">
         <v>18</v>
       </c>
@@ -12130,7 +12126,7 @@
       <c r="Q318"/>
       <c r="R318"/>
     </row>
-    <row r="319" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="11" t="s">
         <v>68</v>
       </c>
@@ -12162,7 +12158,7 @@
       <c r="Q319"/>
       <c r="R319"/>
     </row>
-    <row r="320" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="11" t="s">
         <v>83</v>
       </c>
@@ -12194,7 +12190,7 @@
       <c r="Q320"/>
       <c r="R320"/>
     </row>
-    <row r="321" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="11" t="s">
         <v>85</v>
       </c>
@@ -12226,7 +12222,7 @@
       <c r="Q321"/>
       <c r="R321"/>
     </row>
-    <row r="322" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="11" t="s">
         <v>86</v>
       </c>
@@ -12258,7 +12254,7 @@
       <c r="Q322"/>
       <c r="R322"/>
     </row>
-    <row r="323" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="11" t="s">
         <v>108</v>
       </c>
@@ -12290,7 +12286,7 @@
       <c r="Q323"/>
       <c r="R323"/>
     </row>
-    <row r="324" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="11" t="s">
         <v>111</v>
       </c>
@@ -12322,7 +12318,7 @@
       <c r="Q324"/>
       <c r="R324"/>
     </row>
-    <row r="325" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="11" t="s">
         <v>83</v>
       </c>
@@ -12354,7 +12350,7 @@
       <c r="Q325"/>
       <c r="R325"/>
     </row>
-    <row r="326" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="11" t="s">
         <v>73</v>
       </c>
@@ -12386,7 +12382,7 @@
       <c r="Q326"/>
       <c r="R326"/>
     </row>
-    <row r="327" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="11" t="s">
         <v>84</v>
       </c>
@@ -12418,7 +12414,7 @@
       <c r="Q327"/>
       <c r="R327"/>
     </row>
-    <row r="328" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="11" t="s">
         <v>20</v>
       </c>
@@ -12450,7 +12446,7 @@
       <c r="Q328"/>
       <c r="R328"/>
     </row>
-    <row r="329" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="11" t="s">
         <v>83</v>
       </c>
@@ -12482,7 +12478,7 @@
       <c r="Q329"/>
       <c r="R329"/>
     </row>
-    <row r="330" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="11" t="s">
         <v>73</v>
       </c>
@@ -12514,7 +12510,7 @@
       <c r="Q330"/>
       <c r="R330"/>
     </row>
-    <row r="331" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="11" t="s">
         <v>84</v>
       </c>
@@ -12546,7 +12542,7 @@
       <c r="Q331"/>
       <c r="R331"/>
     </row>
-    <row r="332" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="11" t="s">
         <v>20</v>
       </c>
@@ -12578,7 +12574,7 @@
       <c r="Q332"/>
       <c r="R332"/>
     </row>
-    <row r="333" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="11" t="s">
         <v>73</v>
       </c>
@@ -12610,7 +12606,7 @@
       <c r="Q333"/>
       <c r="R333"/>
     </row>
-    <row r="334" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="11" t="s">
         <v>20</v>
       </c>
@@ -12642,7 +12638,7 @@
       <c r="Q334"/>
       <c r="R334"/>
     </row>
-    <row r="335" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="11" t="s">
         <v>68</v>
       </c>
@@ -12674,7 +12670,7 @@
       <c r="Q335"/>
       <c r="R335"/>
     </row>
-    <row r="336" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="11" t="s">
         <v>86</v>
       </c>
@@ -12706,7 +12702,7 @@
       <c r="Q336"/>
       <c r="R336"/>
     </row>
-    <row r="337" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="11" t="s">
         <v>73</v>
       </c>
@@ -12738,7 +12734,7 @@
       <c r="Q337"/>
       <c r="R337"/>
     </row>
-    <row r="338" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="11" t="s">
         <v>20</v>
       </c>
@@ -12770,7 +12766,7 @@
       <c r="Q338"/>
       <c r="R338"/>
     </row>
-    <row r="339" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="11" t="s">
         <v>85</v>
       </c>
@@ -12802,7 +12798,7 @@
       <c r="Q339"/>
       <c r="R339"/>
     </row>
-    <row r="340" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="11" t="s">
         <v>83</v>
       </c>
@@ -12834,7 +12830,7 @@
       <c r="Q340"/>
       <c r="R340"/>
     </row>
-    <row r="341" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="11" t="s">
         <v>84</v>
       </c>
@@ -12866,7 +12862,7 @@
       <c r="Q341"/>
       <c r="R341"/>
     </row>
-    <row r="342" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="11" t="s">
         <v>108</v>
       </c>
@@ -12898,7 +12894,7 @@
       <c r="Q342"/>
       <c r="R342"/>
     </row>
-    <row r="343" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="11" t="s">
         <v>83</v>
       </c>
@@ -12930,7 +12926,7 @@
       <c r="Q343"/>
       <c r="R343"/>
     </row>
-    <row r="344" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="11" t="s">
         <v>84</v>
       </c>
@@ -12962,7 +12958,7 @@
       <c r="Q344"/>
       <c r="R344"/>
     </row>
-    <row r="345" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="11" t="s">
         <v>73</v>
       </c>
@@ -12994,7 +12990,7 @@
       <c r="Q345"/>
       <c r="R345"/>
     </row>
-    <row r="346" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="11" t="s">
         <v>20</v>
       </c>
@@ -13026,7 +13022,7 @@
       <c r="Q346"/>
       <c r="R346"/>
     </row>
-    <row r="347" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="11" t="s">
         <v>83</v>
       </c>
@@ -13058,7 +13054,7 @@
       <c r="Q347"/>
       <c r="R347"/>
     </row>
-    <row r="348" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="11" t="s">
         <v>84</v>
       </c>
@@ -13090,7 +13086,7 @@
       <c r="Q348"/>
       <c r="R348"/>
     </row>
-    <row r="349" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="11" t="s">
         <v>73</v>
       </c>
@@ -13122,7 +13118,7 @@
       <c r="Q349"/>
       <c r="R349"/>
     </row>
-    <row r="350" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="11" t="s">
         <v>20</v>
       </c>
@@ -13154,7 +13150,7 @@
       <c r="Q350"/>
       <c r="R350"/>
     </row>
-    <row r="351" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
         <v>27</v>
       </c>
@@ -13186,7 +13182,7 @@
       <c r="Q351"/>
       <c r="R351"/>
     </row>
-    <row r="352" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="11" t="s">
         <v>93</v>
       </c>
@@ -13218,7 +13214,7 @@
       <c r="Q352"/>
       <c r="R352"/>
     </row>
-    <row r="353" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="11" t="s">
         <v>73</v>
       </c>
@@ -13250,7 +13246,7 @@
       <c r="Q353"/>
       <c r="R353"/>
     </row>
-    <row r="354" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="11" t="s">
         <v>20</v>
       </c>
@@ -13282,7 +13278,7 @@
       <c r="Q354"/>
       <c r="R354"/>
     </row>
-    <row r="355" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="11" t="s">
         <v>115</v>
       </c>
@@ -13314,7 +13310,7 @@
       <c r="Q355"/>
       <c r="R355"/>
     </row>
-    <row r="356" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="11" t="s">
         <v>84</v>
       </c>
@@ -13346,7 +13342,7 @@
       <c r="Q356"/>
       <c r="R356"/>
     </row>
-    <row r="357" spans="1:20" s="11" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:20" s="11" customFormat="1" ht="15.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="28" t="s">
         <v>25</v>
       </c>
@@ -13378,7 +13374,7 @@
       <c r="Q357"/>
       <c r="R357"/>
     </row>
-    <row r="358" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="11" t="s">
         <v>119</v>
       </c>
@@ -13410,7 +13406,7 @@
       <c r="Q358"/>
       <c r="R358"/>
     </row>
-    <row r="359" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="11" t="s">
         <v>33</v>
       </c>
@@ -13442,7 +13438,7 @@
       <c r="Q359"/>
       <c r="R359"/>
     </row>
-    <row r="360" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B360" s="16"/>
       <c r="C360" s="10"/>
       <c r="F360" s="10"/>
@@ -13456,7 +13452,7 @@
       <c r="O360" s="12"/>
       <c r="P360" s="12"/>
     </row>
-    <row r="361" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="8" t="s">
         <v>1</v>
       </c>
@@ -13470,7 +13466,7 @@
       <c r="O361" s="12"/>
       <c r="P361" s="12"/>
     </row>
-    <row r="362" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="13" t="s">
         <v>3</v>
       </c>
@@ -13484,7 +13480,7 @@
       <c r="O362" s="12"/>
       <c r="P362" s="12"/>
     </row>
-    <row r="363" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="13" t="s">
         <v>11</v>
       </c>
@@ -13498,7 +13494,7 @@
       <c r="O363" s="12"/>
       <c r="P363" s="12"/>
     </row>
-    <row r="364" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="13" t="s">
         <v>4</v>
       </c>
@@ -13512,7 +13508,7 @@
       <c r="O364" s="12"/>
       <c r="P364" s="12"/>
     </row>
-    <row r="365" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="13" t="s">
         <v>2</v>
       </c>
@@ -13526,7 +13522,7 @@
       <c r="O365" s="12"/>
       <c r="P365" s="12"/>
     </row>
-    <row r="366" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="13" t="s">
         <v>6</v>
       </c>
@@ -13540,7 +13536,7 @@
       <c r="O366" s="12"/>
       <c r="P366" s="12"/>
     </row>
-    <row r="367" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="17" t="s">
         <v>7</v>
       </c>
@@ -13560,7 +13556,7 @@
       <c r="O367" s="12"/>
       <c r="P367" s="12"/>
     </row>
-    <row r="368" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="17" t="s">
         <v>8</v>
       </c>
@@ -13598,7 +13594,7 @@
       <c r="S368" s="17"/>
       <c r="T368" s="7"/>
     </row>
-    <row r="369" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="16" t="str">
         <f>B361</f>
         <v>treatment of electrolyzer balance of plant, 1MWe, AEC</v>
@@ -13627,7 +13623,7 @@
       <c r="O369" s="12"/>
       <c r="P369" s="12"/>
     </row>
-    <row r="370" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="16" t="s">
         <v>204</v>
       </c>
@@ -13656,7 +13652,7 @@
       <c r="Q370"/>
       <c r="R370"/>
     </row>
-    <row r="371" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="16" t="s">
         <v>449</v>
       </c>
@@ -13685,7 +13681,7 @@
       <c r="Q371"/>
       <c r="R371"/>
     </row>
-    <row r="372" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="11" t="s">
         <v>206</v>
       </c>
@@ -13714,7 +13710,7 @@
       <c r="Q372"/>
       <c r="R372"/>
     </row>
-    <row r="373" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="11" t="s">
         <v>226</v>
       </c>
@@ -13743,7 +13739,7 @@
       <c r="Q373"/>
       <c r="R373"/>
     </row>
-    <row r="374" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="11" t="s">
         <v>218</v>
       </c>
@@ -13772,7 +13768,7 @@
       <c r="Q374"/>
       <c r="R374"/>
     </row>
-    <row r="375" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="11" t="s">
         <v>219</v>
       </c>
@@ -13801,7 +13797,7 @@
       <c r="Q375"/>
       <c r="R375"/>
     </row>
-    <row r="376" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="11" t="s">
         <v>221</v>
       </c>
@@ -13830,7 +13826,7 @@
       <c r="Q376"/>
       <c r="R376"/>
     </row>
-    <row r="377" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="11" t="s">
         <v>451</v>
       </c>
@@ -13859,7 +13855,7 @@
       <c r="Q377"/>
       <c r="R377"/>
     </row>
-    <row r="378" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="11" t="s">
         <v>208</v>
       </c>
@@ -13888,7 +13884,7 @@
       <c r="Q378"/>
       <c r="R378"/>
     </row>
-    <row r="379" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="11" t="s">
         <v>210</v>
       </c>
@@ -13917,7 +13913,7 @@
       <c r="Q379"/>
       <c r="R379"/>
     </row>
-    <row r="380" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="11" t="s">
         <v>448</v>
       </c>
@@ -13946,7 +13942,7 @@
       <c r="Q380"/>
       <c r="R380"/>
     </row>
-    <row r="381" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B381" s="16"/>
       <c r="K381" s="12"/>
       <c r="L381" s="12"/>
@@ -13955,7 +13951,7 @@
       <c r="O381" s="12"/>
       <c r="P381" s="12"/>
     </row>
-    <row r="382" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="8" t="s">
         <v>1</v>
       </c>
@@ -13970,7 +13966,7 @@
       <c r="O382" s="12"/>
       <c r="P382" s="12"/>
     </row>
-    <row r="383" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="13" t="s">
         <v>3</v>
       </c>
@@ -13984,7 +13980,7 @@
       <c r="O383" s="12"/>
       <c r="P383" s="12"/>
     </row>
-    <row r="384" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="13" t="s">
         <v>11</v>
       </c>
@@ -13998,7 +13994,7 @@
       <c r="O384" s="12"/>
       <c r="P384" s="12"/>
     </row>
-    <row r="385" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="13" t="s">
         <v>4</v>
       </c>
@@ -14012,7 +14008,7 @@
       <c r="O385" s="12"/>
       <c r="P385" s="12"/>
     </row>
-    <row r="386" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="13" t="s">
         <v>2</v>
       </c>
@@ -14026,7 +14022,7 @@
       <c r="O386" s="12"/>
       <c r="P386" s="12"/>
     </row>
-    <row r="387" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="13" t="s">
         <v>6</v>
       </c>
@@ -14043,7 +14039,7 @@
       <c r="O387" s="12"/>
       <c r="P387" s="12"/>
     </row>
-    <row r="388" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="17" t="s">
         <v>7</v>
       </c>
@@ -14063,7 +14059,7 @@
       <c r="O388" s="12"/>
       <c r="P388" s="12"/>
     </row>
-    <row r="389" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="17" t="s">
         <v>8</v>
       </c>
@@ -14128,7 +14124,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="390" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="16" t="s">
         <v>441</v>
       </c>
@@ -14160,7 +14156,7 @@
       <c r="P390" s="12"/>
       <c r="T390"/>
     </row>
-    <row r="391" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="16" t="str">
         <f>B424</f>
         <v>electrolyzer production, 1MWe, SOEC, Stack</v>
@@ -14194,7 +14190,7 @@
       <c r="Q391"/>
       <c r="R391"/>
     </row>
-    <row r="392" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="16" t="str">
         <f>B461</f>
         <v>electrolyzer production, 1MWe, SOEC, Balance of Plant</v>
@@ -14228,7 +14224,7 @@
       <c r="Q392"/>
       <c r="R392"/>
     </row>
-    <row r="393" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="16" t="s">
         <v>513</v>
       </c>
@@ -14261,7 +14257,7 @@
       <c r="Q393"/>
       <c r="R393"/>
     </row>
-    <row r="394" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="16" t="s">
         <v>515</v>
       </c>
@@ -14294,7 +14290,7 @@
       <c r="Q394"/>
       <c r="R394"/>
     </row>
-    <row r="395" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="13" t="s">
         <v>50</v>
       </c>
@@ -14339,7 +14335,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="396" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="13" t="s">
         <v>51</v>
       </c>
@@ -14372,7 +14368,7 @@
       <c r="Q396"/>
       <c r="R396"/>
     </row>
-    <row r="397" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="13" t="s">
         <v>517</v>
       </c>
@@ -14404,7 +14400,7 @@
       <c r="Q397"/>
       <c r="R397"/>
     </row>
-    <row r="398" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="21" t="s">
         <v>38</v>
       </c>
@@ -14433,7 +14429,7 @@
       <c r="Q398" s="19"/>
       <c r="R398"/>
     </row>
-    <row r="399" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="47" t="s">
         <v>456</v>
       </c>
@@ -14497,7 +14493,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="400" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="47" t="s">
         <v>458</v>
       </c>
@@ -14551,7 +14547,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="401" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="47" t="s">
         <v>461</v>
       </c>
@@ -14605,7 +14601,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="402" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B402" s="16"/>
       <c r="K402" s="12"/>
       <c r="L402" s="12"/>
@@ -14614,7 +14610,7 @@
       <c r="O402" s="12"/>
       <c r="P402" s="12"/>
     </row>
-    <row r="403" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="8" t="s">
         <v>1</v>
       </c>
@@ -14629,7 +14625,7 @@
       <c r="O403" s="12"/>
       <c r="P403" s="12"/>
     </row>
-    <row r="404" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="13" t="s">
         <v>3</v>
       </c>
@@ -14643,7 +14639,7 @@
       <c r="O404" s="12"/>
       <c r="P404" s="12"/>
     </row>
-    <row r="405" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="13" t="s">
         <v>11</v>
       </c>
@@ -14657,7 +14653,7 @@
       <c r="O405" s="12"/>
       <c r="P405" s="12"/>
     </row>
-    <row r="406" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="13" t="s">
         <v>4</v>
       </c>
@@ -14671,7 +14667,7 @@
       <c r="O406" s="12"/>
       <c r="P406" s="12"/>
     </row>
-    <row r="407" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="13" t="s">
         <v>2</v>
       </c>
@@ -14685,7 +14681,7 @@
       <c r="O407" s="12"/>
       <c r="P407" s="12"/>
     </row>
-    <row r="408" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="13" t="s">
         <v>6</v>
       </c>
@@ -14702,7 +14698,7 @@
       <c r="O408" s="12"/>
       <c r="P408" s="12"/>
     </row>
-    <row r="409" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="17" t="s">
         <v>7</v>
       </c>
@@ -14722,7 +14718,7 @@
       <c r="O409" s="12"/>
       <c r="P409" s="12"/>
     </row>
-    <row r="410" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="17" t="s">
         <v>8</v>
       </c>
@@ -14787,7 +14783,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="411" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="16" t="s">
         <v>445</v>
       </c>
@@ -14819,7 +14815,7 @@
       <c r="P411" s="12"/>
       <c r="T411"/>
     </row>
-    <row r="412" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="16" t="s">
         <v>153</v>
       </c>
@@ -14866,7 +14862,7 @@
         <v>2.8248587570621469E-6</v>
       </c>
     </row>
-    <row r="413" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="16" t="s">
         <v>179</v>
       </c>
@@ -14913,7 +14909,7 @@
         <v>3.5310734463276836E-7</v>
       </c>
     </row>
-    <row r="414" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="16" t="s">
         <v>513</v>
       </c>
@@ -14963,7 +14959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="16" t="s">
         <v>515</v>
       </c>
@@ -15013,7 +15009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="13" t="s">
         <v>50</v>
       </c>
@@ -15046,7 +15042,7 @@
       <c r="Q416"/>
       <c r="R416"/>
     </row>
-    <row r="417" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="13" t="s">
         <v>51</v>
       </c>
@@ -15079,7 +15075,7 @@
       <c r="Q417"/>
       <c r="R417"/>
     </row>
-    <row r="418" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="13" t="s">
         <v>517</v>
       </c>
@@ -15111,7 +15107,7 @@
       <c r="Q418"/>
       <c r="R418"/>
     </row>
-    <row r="419" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="21" t="s">
         <v>38</v>
       </c>
@@ -15140,7 +15136,7 @@
       <c r="Q419" s="19"/>
       <c r="R419"/>
     </row>
-    <row r="420" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="47" t="s">
         <v>456</v>
       </c>
@@ -15204,7 +15200,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="421" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="47" t="s">
         <v>458</v>
       </c>
@@ -15258,7 +15254,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="422" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="47" t="s">
         <v>461</v>
       </c>
@@ -15312,7 +15308,7 @@
         <v>0.24634371748562628</v>
       </c>
     </row>
-    <row r="423" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B423" s="16"/>
       <c r="K423" s="12"/>
       <c r="L423" s="12"/>
@@ -15321,7 +15317,7 @@
       <c r="O423" s="12"/>
       <c r="P423" s="12"/>
     </row>
-    <row r="424" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="8" t="s">
         <v>1</v>
       </c>
@@ -15335,7 +15331,7 @@
       <c r="O424" s="12"/>
       <c r="P424" s="12"/>
     </row>
-    <row r="425" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="13" t="s">
         <v>3</v>
       </c>
@@ -15349,7 +15345,7 @@
       <c r="O425" s="12"/>
       <c r="P425" s="12"/>
     </row>
-    <row r="426" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="13" t="s">
         <v>11</v>
       </c>
@@ -15363,7 +15359,7 @@
       <c r="O426" s="12"/>
       <c r="P426" s="12"/>
     </row>
-    <row r="427" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="13" t="s">
         <v>4</v>
       </c>
@@ -15377,7 +15373,7 @@
       <c r="O427" s="12"/>
       <c r="P427" s="12"/>
     </row>
-    <row r="428" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="13" t="s">
         <v>2</v>
       </c>
@@ -15391,7 +15387,7 @@
       <c r="O428" s="12"/>
       <c r="P428" s="12"/>
     </row>
-    <row r="429" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="13" t="s">
         <v>6</v>
       </c>
@@ -15405,7 +15401,7 @@
       <c r="O429" s="12"/>
       <c r="P429" s="12"/>
     </row>
-    <row r="430" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="17" t="s">
         <v>7</v>
       </c>
@@ -15425,7 +15421,7 @@
       <c r="O430" s="12"/>
       <c r="P430" s="12"/>
     </row>
-    <row r="431" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="17" t="s">
         <v>8</v>
       </c>
@@ -15463,7 +15459,7 @@
       <c r="S431" s="17"/>
       <c r="T431" s="7"/>
     </row>
-    <row r="432" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="16" t="str">
         <f>B424</f>
         <v>electrolyzer production, 1MWe, SOEC, Stack</v>
@@ -15492,7 +15488,7 @@
       <c r="O432" s="12"/>
       <c r="P432" s="12"/>
     </row>
-    <row r="433" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="11" t="s">
         <v>73</v>
       </c>
@@ -15524,7 +15520,7 @@
       <c r="Q433"/>
       <c r="R433"/>
     </row>
-    <row r="434" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="11" t="s">
         <v>20</v>
       </c>
@@ -15556,7 +15552,7 @@
       <c r="Q434"/>
       <c r="R434"/>
     </row>
-    <row r="435" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="11" t="s">
         <v>155</v>
       </c>
@@ -15588,7 +15584,7 @@
       <c r="Q435"/>
       <c r="R435"/>
     </row>
-    <row r="436" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="11" t="s">
         <v>131</v>
       </c>
@@ -15620,7 +15616,7 @@
       <c r="Q436"/>
       <c r="R436"/>
     </row>
-    <row r="437" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="11" t="s">
         <v>136</v>
       </c>
@@ -15652,7 +15648,7 @@
       <c r="Q437"/>
       <c r="R437"/>
     </row>
-    <row r="438" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="11" t="s">
         <v>159</v>
       </c>
@@ -15684,7 +15680,7 @@
       <c r="Q438"/>
       <c r="R438"/>
     </row>
-    <row r="439" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="11" t="s">
         <v>161</v>
       </c>
@@ -15716,7 +15712,7 @@
       <c r="Q439"/>
       <c r="R439"/>
     </row>
-    <row r="440" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="11" t="s">
         <v>159</v>
       </c>
@@ -15748,7 +15744,7 @@
       <c r="Q440"/>
       <c r="R440"/>
     </row>
-    <row r="441" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="11" t="s">
         <v>163</v>
       </c>
@@ -15781,7 +15777,7 @@
       <c r="Q441"/>
       <c r="R441"/>
     </row>
-    <row r="442" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="11" t="s">
         <v>166</v>
       </c>
@@ -15814,7 +15810,7 @@
       <c r="Q442"/>
       <c r="R442"/>
     </row>
-    <row r="443" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="11" t="s">
         <v>168</v>
       </c>
@@ -15846,7 +15842,7 @@
       <c r="Q443"/>
       <c r="R443"/>
     </row>
-    <row r="444" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="11" t="s">
         <v>172</v>
       </c>
@@ -15878,7 +15874,7 @@
       <c r="Q444"/>
       <c r="R444"/>
     </row>
-    <row r="445" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="11" t="s">
         <v>174</v>
       </c>
@@ -15910,7 +15906,7 @@
       <c r="Q445"/>
       <c r="R445"/>
     </row>
-    <row r="446" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="11" t="s">
         <v>176</v>
       </c>
@@ -15942,7 +15938,7 @@
       <c r="Q446"/>
       <c r="R446"/>
     </row>
-    <row r="447" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="11" t="s">
         <v>131</v>
       </c>
@@ -15974,7 +15970,7 @@
       <c r="Q447"/>
       <c r="R447"/>
     </row>
-    <row r="448" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="11" t="s">
         <v>33</v>
       </c>
@@ -16006,7 +16002,7 @@
       <c r="Q448"/>
       <c r="R448"/>
     </row>
-    <row r="449" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B449" s="12"/>
       <c r="F449" s="10"/>
       <c r="G449" s="10"/>
@@ -16017,7 +16013,7 @@
       <c r="O449" s="12"/>
       <c r="P449" s="12"/>
     </row>
-    <row r="450" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="8" t="s">
         <v>1</v>
       </c>
@@ -16031,7 +16027,7 @@
       <c r="O450" s="12"/>
       <c r="P450" s="12"/>
     </row>
-    <row r="451" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="13" t="s">
         <v>3</v>
       </c>
@@ -16045,7 +16041,7 @@
       <c r="O451" s="12"/>
       <c r="P451" s="12"/>
     </row>
-    <row r="452" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="13" t="s">
         <v>11</v>
       </c>
@@ -16059,7 +16055,7 @@
       <c r="O452" s="12"/>
       <c r="P452" s="12"/>
     </row>
-    <row r="453" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="13" t="s">
         <v>4</v>
       </c>
@@ -16073,7 +16069,7 @@
       <c r="O453" s="12"/>
       <c r="P453" s="12"/>
     </row>
-    <row r="454" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="13" t="s">
         <v>2</v>
       </c>
@@ -16087,7 +16083,7 @@
       <c r="O454" s="12"/>
       <c r="P454" s="12"/>
     </row>
-    <row r="455" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="13" t="s">
         <v>6</v>
       </c>
@@ -16101,7 +16097,7 @@
       <c r="O455" s="12"/>
       <c r="P455" s="12"/>
     </row>
-    <row r="456" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="17" t="s">
         <v>7</v>
       </c>
@@ -16121,7 +16117,7 @@
       <c r="O456" s="12"/>
       <c r="P456" s="12"/>
     </row>
-    <row r="457" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="17" t="s">
         <v>8</v>
       </c>
@@ -16159,7 +16155,7 @@
       <c r="S457" s="17"/>
       <c r="T457" s="7"/>
     </row>
-    <row r="458" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="16" t="str">
         <f>B450</f>
         <v>treatment of electrolyzer stack, 1MWe, SOEC</v>
@@ -16188,7 +16184,7 @@
       <c r="O458" s="12"/>
       <c r="P458" s="12"/>
     </row>
-    <row r="459" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="16" t="s">
         <v>204</v>
       </c>
@@ -16217,7 +16213,7 @@
       <c r="Q459"/>
       <c r="R459"/>
     </row>
-    <row r="460" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B460" s="16"/>
       <c r="K460" s="12"/>
       <c r="L460" s="12"/>
@@ -16226,7 +16222,7 @@
       <c r="O460" s="12"/>
       <c r="P460" s="12"/>
     </row>
-    <row r="461" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="8" t="s">
         <v>1</v>
       </c>
@@ -16240,7 +16236,7 @@
       <c r="O461" s="12"/>
       <c r="P461" s="12"/>
     </row>
-    <row r="462" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="13" t="s">
         <v>3</v>
       </c>
@@ -16254,7 +16250,7 @@
       <c r="O462" s="12"/>
       <c r="P462" s="12"/>
     </row>
-    <row r="463" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="13" t="s">
         <v>11</v>
       </c>
@@ -16268,7 +16264,7 @@
       <c r="O463" s="12"/>
       <c r="P463" s="12"/>
     </row>
-    <row r="464" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="13" t="s">
         <v>4</v>
       </c>
@@ -16282,7 +16278,7 @@
       <c r="O464" s="12"/>
       <c r="P464" s="12"/>
     </row>
-    <row r="465" spans="1:20" s="11" customFormat="1" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:20" s="11" customFormat="1" ht="16.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="13" t="s">
         <v>2</v>
       </c>
@@ -16296,7 +16292,7 @@
       <c r="O465" s="12"/>
       <c r="P465" s="12"/>
     </row>
-    <row r="466" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="13" t="s">
         <v>6</v>
       </c>
@@ -16312,7 +16308,7 @@
       <c r="O466" s="12"/>
       <c r="P466" s="12"/>
     </row>
-    <row r="467" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="17" t="s">
         <v>7</v>
       </c>
@@ -16331,7 +16327,7 @@
       <c r="O467" s="12"/>
       <c r="P467" s="12"/>
     </row>
-    <row r="468" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="17" t="s">
         <v>8</v>
       </c>
@@ -16369,7 +16365,7 @@
       <c r="S468" s="17"/>
       <c r="T468" s="7"/>
     </row>
-    <row r="469" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="16" t="str">
         <f>B461</f>
         <v>electrolyzer production, 1MWe, SOEC, Balance of Plant</v>
@@ -16400,7 +16396,7 @@
       <c r="O469" s="12"/>
       <c r="P469" s="12"/>
     </row>
-    <row r="470" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="11" t="s">
         <v>73</v>
       </c>
@@ -16432,7 +16428,7 @@
       <c r="Q470"/>
       <c r="R470"/>
     </row>
-    <row r="471" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="11" t="s">
         <v>20</v>
       </c>
@@ -16464,7 +16460,7 @@
       <c r="Q471"/>
       <c r="R471"/>
     </row>
-    <row r="472" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="16" t="s">
         <v>18</v>
       </c>
@@ -16496,7 +16492,7 @@
       <c r="Q472"/>
       <c r="R472"/>
     </row>
-    <row r="473" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="16" t="s">
         <v>68</v>
       </c>
@@ -16528,7 +16524,7 @@
       <c r="Q473"/>
       <c r="R473"/>
     </row>
-    <row r="474" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="16" t="s">
         <v>83</v>
       </c>
@@ -16561,7 +16557,7 @@
       <c r="Q474"/>
       <c r="R474"/>
     </row>
-    <row r="475" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="16" t="s">
         <v>85</v>
       </c>
@@ -16594,7 +16590,7 @@
       <c r="Q475"/>
       <c r="R475"/>
     </row>
-    <row r="476" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="16" t="s">
         <v>86</v>
       </c>
@@ -16627,7 +16623,7 @@
       <c r="Q476"/>
       <c r="R476"/>
     </row>
-    <row r="477" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="16" t="s">
         <v>108</v>
       </c>
@@ -16660,7 +16656,7 @@
       <c r="Q477"/>
       <c r="R477"/>
     </row>
-    <row r="478" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="16" t="s">
         <v>111</v>
       </c>
@@ -16693,7 +16689,7 @@
       <c r="Q478"/>
       <c r="R478"/>
     </row>
-    <row r="479" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="16" t="s">
         <v>83</v>
       </c>
@@ -16726,7 +16722,7 @@
       <c r="Q479"/>
       <c r="R479"/>
     </row>
-    <row r="480" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="16" t="s">
         <v>73</v>
       </c>
@@ -16759,7 +16755,7 @@
       <c r="Q480"/>
       <c r="R480"/>
     </row>
-    <row r="481" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="16" t="s">
         <v>84</v>
       </c>
@@ -16792,7 +16788,7 @@
       <c r="Q481"/>
       <c r="R481"/>
     </row>
-    <row r="482" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="16" t="s">
         <v>20</v>
       </c>
@@ -16825,7 +16821,7 @@
       <c r="Q482"/>
       <c r="R482"/>
     </row>
-    <row r="483" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="16" t="s">
         <v>83</v>
       </c>
@@ -16858,7 +16854,7 @@
       <c r="Q483"/>
       <c r="R483"/>
     </row>
-    <row r="484" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="16" t="s">
         <v>73</v>
       </c>
@@ -16891,7 +16887,7 @@
       <c r="Q484"/>
       <c r="R484"/>
     </row>
-    <row r="485" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="16" t="s">
         <v>84</v>
       </c>
@@ -16924,7 +16920,7 @@
       <c r="Q485"/>
       <c r="R485"/>
     </row>
-    <row r="486" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="16" t="s">
         <v>20</v>
       </c>
@@ -16957,7 +16953,7 @@
       <c r="Q486"/>
       <c r="R486"/>
     </row>
-    <row r="487" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="16" t="s">
         <v>18</v>
       </c>
@@ -16989,7 +16985,7 @@
       <c r="Q487"/>
       <c r="R487"/>
     </row>
-    <row r="488" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="16" t="s">
         <v>68</v>
       </c>
@@ -17021,7 +17017,7 @@
       <c r="Q488"/>
       <c r="R488"/>
     </row>
-    <row r="489" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="16" t="s">
         <v>83</v>
       </c>
@@ -17053,7 +17049,7 @@
       <c r="Q489"/>
       <c r="R489"/>
     </row>
-    <row r="490" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="16" t="s">
         <v>58</v>
       </c>
@@ -17085,7 +17081,7 @@
       <c r="Q490"/>
       <c r="R490"/>
     </row>
-    <row r="491" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="16" t="s">
         <v>84</v>
       </c>
@@ -17117,7 +17113,7 @@
       <c r="Q491"/>
       <c r="R491"/>
     </row>
-    <row r="492" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="16" t="s">
         <v>85</v>
       </c>
@@ -17149,7 +17145,7 @@
       <c r="Q492"/>
       <c r="R492"/>
     </row>
-    <row r="493" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="16" t="s">
         <v>86</v>
       </c>
@@ -17181,7 +17177,7 @@
       <c r="Q493"/>
       <c r="R493"/>
     </row>
-    <row r="494" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="16" t="s">
         <v>30</v>
       </c>
@@ -17213,7 +17209,7 @@
       <c r="Q494"/>
       <c r="R494"/>
     </row>
-    <row r="495" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="16" t="s">
         <v>73</v>
       </c>
@@ -17246,7 +17242,7 @@
       <c r="Q495"/>
       <c r="R495"/>
     </row>
-    <row r="496" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="16" t="s">
         <v>20</v>
       </c>
@@ -17279,7 +17275,7 @@
       <c r="Q496"/>
       <c r="R496"/>
     </row>
-    <row r="497" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="16" t="s">
         <v>73</v>
       </c>
@@ -17311,7 +17307,7 @@
       <c r="Q497"/>
       <c r="R497"/>
     </row>
-    <row r="498" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="16" t="s">
         <v>20</v>
       </c>
@@ -17343,7 +17339,7 @@
       <c r="Q498"/>
       <c r="R498"/>
     </row>
-    <row r="499" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="16" t="s">
         <v>73</v>
       </c>
@@ -17376,7 +17372,7 @@
       <c r="Q499"/>
       <c r="R499"/>
     </row>
-    <row r="500" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="16" t="s">
         <v>20</v>
       </c>
@@ -17409,7 +17405,7 @@
       <c r="Q500"/>
       <c r="R500"/>
     </row>
-    <row r="501" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="16" t="s">
         <v>73</v>
       </c>
@@ -17442,7 +17438,7 @@
       <c r="Q501"/>
       <c r="R501"/>
     </row>
-    <row r="502" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="16" t="s">
         <v>20</v>
       </c>
@@ -17475,7 +17471,7 @@
       <c r="Q502"/>
       <c r="R502"/>
     </row>
-    <row r="503" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="16" t="s">
         <v>191</v>
       </c>
@@ -17508,7 +17504,7 @@
       <c r="Q503"/>
       <c r="R503"/>
     </row>
-    <row r="504" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="16" t="s">
         <v>93</v>
       </c>
@@ -17541,7 +17537,7 @@
       <c r="Q504"/>
       <c r="R504"/>
     </row>
-    <row r="505" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" s="16" t="s">
         <v>85</v>
       </c>
@@ -17574,7 +17570,7 @@
       <c r="Q505"/>
       <c r="R505"/>
     </row>
-    <row r="506" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" s="16" t="s">
         <v>68</v>
       </c>
@@ -17607,7 +17603,7 @@
       <c r="Q506"/>
       <c r="R506"/>
     </row>
-    <row r="507" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" s="16" t="s">
         <v>86</v>
       </c>
@@ -17640,7 +17636,7 @@
       <c r="Q507"/>
       <c r="R507"/>
     </row>
-    <row r="508" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="16" t="s">
         <v>83</v>
       </c>
@@ -17673,7 +17669,7 @@
       <c r="Q508"/>
       <c r="R508"/>
     </row>
-    <row r="509" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="16" t="s">
         <v>84</v>
       </c>
@@ -17706,7 +17702,7 @@
       <c r="Q509"/>
       <c r="R509"/>
     </row>
-    <row r="510" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="16" t="s">
         <v>83</v>
       </c>
@@ -17739,7 +17735,7 @@
       <c r="Q510"/>
       <c r="R510"/>
     </row>
-    <row r="511" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="16" t="s">
         <v>84</v>
       </c>
@@ -17772,7 +17768,7 @@
       <c r="Q511"/>
       <c r="R511"/>
     </row>
-    <row r="512" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="16" t="s">
         <v>83</v>
       </c>
@@ -17804,7 +17800,7 @@
       <c r="Q512"/>
       <c r="R512"/>
     </row>
-    <row r="513" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="16" t="s">
         <v>84</v>
       </c>
@@ -17836,7 +17832,7 @@
       <c r="Q513"/>
       <c r="R513"/>
     </row>
-    <row r="514" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="16" t="s">
         <v>83</v>
       </c>
@@ -17868,7 +17864,7 @@
       <c r="Q514"/>
       <c r="R514"/>
     </row>
-    <row r="515" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="16" t="s">
         <v>84</v>
       </c>
@@ -17900,7 +17896,7 @@
       <c r="Q515"/>
       <c r="R515"/>
     </row>
-    <row r="516" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="16" t="s">
         <v>18</v>
       </c>
@@ -17932,7 +17928,7 @@
       <c r="Q516"/>
       <c r="R516"/>
     </row>
-    <row r="517" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="16" t="s">
         <v>68</v>
       </c>
@@ -17964,7 +17960,7 @@
       <c r="Q517"/>
       <c r="R517"/>
     </row>
-    <row r="518" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="16" t="s">
         <v>83</v>
       </c>
@@ -17996,7 +17992,7 @@
       <c r="Q518"/>
       <c r="R518"/>
     </row>
-    <row r="519" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="16" t="s">
         <v>85</v>
       </c>
@@ -18028,7 +18024,7 @@
       <c r="Q519"/>
       <c r="R519"/>
     </row>
-    <row r="520" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="16" t="s">
         <v>86</v>
       </c>
@@ -18060,7 +18056,7 @@
       <c r="Q520"/>
       <c r="R520"/>
     </row>
-    <row r="521" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="16" t="s">
         <v>25</v>
       </c>
@@ -18092,7 +18088,7 @@
       <c r="Q521"/>
       <c r="R521"/>
     </row>
-    <row r="522" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" s="16" t="s">
         <v>84</v>
       </c>
@@ -18124,7 +18120,7 @@
       <c r="Q522"/>
       <c r="R522"/>
     </row>
-    <row r="523" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" s="16" t="s">
         <v>102</v>
       </c>
@@ -18156,7 +18152,7 @@
       <c r="Q523"/>
       <c r="R523"/>
     </row>
-    <row r="524" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="16" t="s">
         <v>105</v>
       </c>
@@ -18188,7 +18184,7 @@
       <c r="Q524"/>
       <c r="R524"/>
     </row>
-    <row r="525" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="16" t="s">
         <v>83</v>
       </c>
@@ -18220,7 +18216,7 @@
       <c r="Q525"/>
       <c r="R525"/>
     </row>
-    <row r="526" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" s="16" t="s">
         <v>84</v>
       </c>
@@ -18252,7 +18248,7 @@
       <c r="Q526"/>
       <c r="R526"/>
     </row>
-    <row r="527" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="16" t="s">
         <v>73</v>
       </c>
@@ -18284,7 +18280,7 @@
       <c r="Q527"/>
       <c r="R527"/>
     </row>
-    <row r="528" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" s="16" t="s">
         <v>20</v>
       </c>
@@ -18316,7 +18312,7 @@
       <c r="Q528"/>
       <c r="R528"/>
     </row>
-    <row r="529" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="16" t="s">
         <v>115</v>
       </c>
@@ -18348,7 +18344,7 @@
       <c r="Q529"/>
       <c r="R529"/>
     </row>
-    <row r="530" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="16" t="s">
         <v>84</v>
       </c>
@@ -18380,7 +18376,7 @@
       <c r="Q530"/>
       <c r="R530"/>
     </row>
-    <row r="531" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="16" t="s">
         <v>201</v>
       </c>
@@ -18412,7 +18408,7 @@
       <c r="Q531"/>
       <c r="R531"/>
     </row>
-    <row r="532" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="16" t="s">
         <v>119</v>
       </c>
@@ -18444,7 +18440,7 @@
       <c r="Q532"/>
       <c r="R532"/>
     </row>
-    <row r="533" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="11" t="s">
         <v>33</v>
       </c>
@@ -18476,7 +18472,7 @@
       <c r="Q533"/>
       <c r="R533"/>
     </row>
-    <row r="534" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B534" s="16"/>
       <c r="F534" s="10"/>
       <c r="G534" s="10"/>
@@ -18487,7 +18483,7 @@
       <c r="O534" s="12"/>
       <c r="P534" s="12"/>
     </row>
-    <row r="535" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" s="8" t="s">
         <v>1</v>
       </c>
@@ -18501,7 +18497,7 @@
       <c r="O535" s="12"/>
       <c r="P535" s="12"/>
     </row>
-    <row r="536" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" s="13" t="s">
         <v>3</v>
       </c>
@@ -18515,7 +18511,7 @@
       <c r="O536" s="12"/>
       <c r="P536" s="12"/>
     </row>
-    <row r="537" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="13" t="s">
         <v>11</v>
       </c>
@@ -18529,7 +18525,7 @@
       <c r="O537" s="12"/>
       <c r="P537" s="12"/>
     </row>
-    <row r="538" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="13" t="s">
         <v>4</v>
       </c>
@@ -18543,7 +18539,7 @@
       <c r="O538" s="12"/>
       <c r="P538" s="12"/>
     </row>
-    <row r="539" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="13" t="s">
         <v>2</v>
       </c>
@@ -18557,7 +18553,7 @@
       <c r="O539" s="12"/>
       <c r="P539" s="12"/>
     </row>
-    <row r="540" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="13" t="s">
         <v>6</v>
       </c>
@@ -18571,7 +18567,7 @@
       <c r="O540" s="12"/>
       <c r="P540" s="12"/>
     </row>
-    <row r="541" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="17" t="s">
         <v>7</v>
       </c>
@@ -18591,7 +18587,7 @@
       <c r="O541" s="12"/>
       <c r="P541" s="12"/>
     </row>
-    <row r="542" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="17" t="s">
         <v>8</v>
       </c>
@@ -18629,7 +18625,7 @@
       <c r="S542" s="17"/>
       <c r="T542" s="7"/>
     </row>
-    <row r="543" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="16" t="str">
         <f>B535</f>
         <v>treatment of electrolyzer balance of plant, 1MWe, SOEC</v>
@@ -18658,7 +18654,7 @@
       <c r="O543" s="12"/>
       <c r="P543" s="12"/>
     </row>
-    <row r="544" spans="1:20" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:20" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="16" t="s">
         <v>204</v>
       </c>
@@ -18687,7 +18683,7 @@
       <c r="Q544"/>
       <c r="R544"/>
     </row>
-    <row r="545" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="16" t="s">
         <v>449</v>
       </c>
@@ -18716,7 +18712,7 @@
       <c r="Q545"/>
       <c r="R545"/>
     </row>
-    <row r="546" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" s="11" t="s">
         <v>206</v>
       </c>
@@ -18745,7 +18741,7 @@
       <c r="Q546"/>
       <c r="R546"/>
     </row>
-    <row r="547" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" s="11" t="s">
         <v>226</v>
       </c>
@@ -18774,7 +18770,7 @@
       <c r="Q547"/>
       <c r="R547"/>
     </row>
-    <row r="548" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" s="11" t="s">
         <v>218</v>
       </c>
@@ -18803,7 +18799,7 @@
       <c r="Q548"/>
       <c r="R548"/>
     </row>
-    <row r="549" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="11" t="s">
         <v>219</v>
       </c>
@@ -18832,7 +18828,7 @@
       <c r="Q549"/>
       <c r="R549"/>
     </row>
-    <row r="550" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="11" t="s">
         <v>221</v>
       </c>
@@ -18861,7 +18857,7 @@
       <c r="Q550"/>
       <c r="R550"/>
     </row>
-    <row r="551" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" s="11" t="s">
         <v>451</v>
       </c>
@@ -18890,7 +18886,7 @@
       <c r="Q551"/>
       <c r="R551"/>
     </row>
-    <row r="552" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" s="11" t="s">
         <v>208</v>
       </c>
@@ -18919,7 +18915,7 @@
       <c r="Q552"/>
       <c r="R552"/>
     </row>
-    <row r="553" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="11" t="s">
         <v>210</v>
       </c>
@@ -18948,7 +18944,7 @@
       <c r="Q553"/>
       <c r="R553"/>
     </row>
-    <row r="554" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="11" t="s">
         <v>448</v>
       </c>
@@ -18977,7 +18973,7 @@
       <c r="Q554"/>
       <c r="R554"/>
     </row>
-    <row r="555" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="B555" s="16"/>
       <c r="K555" s="12"/>
       <c r="L555" s="12"/>
@@ -18986,7 +18982,7 @@
       <c r="O555" s="12"/>
       <c r="P555" s="12"/>
     </row>
-    <row r="556" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="8" t="s">
         <v>1</v>
       </c>
@@ -19001,7 +18997,7 @@
       <c r="O556" s="12"/>
       <c r="P556" s="12"/>
     </row>
-    <row r="557" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="13" t="s">
         <v>3</v>
       </c>
@@ -19015,12 +19011,12 @@
       <c r="O557" s="12"/>
       <c r="P557" s="12"/>
     </row>
-    <row r="558" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B558" s="14" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K558" s="12"/>
       <c r="L558" s="12"/>
@@ -19029,7 +19025,7 @@
       <c r="O558" s="12"/>
       <c r="P558" s="12"/>
     </row>
-    <row r="559" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="13" t="s">
         <v>4</v>
       </c>
@@ -19043,7 +19039,7 @@
       <c r="O559" s="12"/>
       <c r="P559" s="12"/>
     </row>
-    <row r="560" spans="1:18" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:18" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="13" t="s">
         <v>2</v>
       </c>
@@ -19057,7 +19053,7 @@
       <c r="O560" s="12"/>
       <c r="P560" s="12"/>
     </row>
-    <row r="561" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="13" t="s">
         <v>6</v>
       </c>
@@ -19074,7 +19070,7 @@
       <c r="O561" s="12"/>
       <c r="P561" s="12"/>
     </row>
-    <row r="562" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="17" t="s">
         <v>7</v>
       </c>
@@ -19094,7 +19090,7 @@
       <c r="O562" s="12"/>
       <c r="P562" s="12"/>
     </row>
-    <row r="563" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="17" t="s">
         <v>8</v>
       </c>
@@ -19159,7 +19155,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="564" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="16" t="str">
         <f>B556</f>
         <v>deionized water production, via reverse osmosis, from brackish water</v>
@@ -19195,7 +19191,7 @@
       <c r="P564" s="12"/>
       <c r="T564"/>
     </row>
-    <row r="565" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>33</v>
       </c>
@@ -19215,12 +19211,12 @@
         <v>36</v>
       </c>
       <c r="H565" t="s">
-        <v>531</v>
-      </c>
-      <c r="I565" s="60">
+        <v>530</v>
+      </c>
+      <c r="I565">
         <v>5</v>
       </c>
-      <c r="J565" s="61">
+      <c r="J565" s="4">
         <f>B565</f>
         <v>1.5499999999999999E-3</v>
       </c>
@@ -19233,7 +19229,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
     </row>
-    <row r="566" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>519</v>
       </c>
@@ -19252,11 +19248,11 @@
       <c r="G566" t="s">
         <v>520</v>
       </c>
-      <c r="I566" s="60">
+      <c r="I566">
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>521</v>
       </c>
@@ -19264,7 +19260,7 @@
         <v>7.5799999999999998E-7</v>
       </c>
       <c r="C567" s="11" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D567" t="s">
         <v>13</v>
@@ -19275,11 +19271,11 @@
       <c r="G567" t="s">
         <v>522</v>
       </c>
-      <c r="I567" s="60">
+      <c r="I567">
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>523</v>
       </c>
@@ -19298,13 +19294,13 @@
       <c r="G568" t="s">
         <v>524</v>
       </c>
-      <c r="I568" s="62">
+      <c r="I568">
         <v>0</v>
       </c>
     </row>
     <row r="569" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B569" s="4">
         <v>2.7E-6</v>
@@ -19319,15 +19315,15 @@
         <v>12</v>
       </c>
       <c r="G569" t="s">
+        <v>525</v>
+      </c>
+      <c r="I569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A570" t="s">
         <v>526</v>
-      </c>
-      <c r="I569" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="570" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A570" t="s">
-        <v>527</v>
       </c>
       <c r="B570" s="4">
         <f>1/0.7/1000</f>
@@ -19337,18 +19333,18 @@
         <v>31</v>
       </c>
       <c r="E570" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F570" t="s">
         <v>14</v>
       </c>
       <c r="H570" t="s">
-        <v>529</v>
-      </c>
-      <c r="I570" s="62">
+        <v>528</v>
+      </c>
+      <c r="I570">
         <v>5</v>
       </c>
-      <c r="J570" s="61">
+      <c r="J570" s="4">
         <f>B570</f>
         <v>1.4285714285714286E-3</v>
       </c>
@@ -19361,9 +19357,9 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="571" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B571" s="4">
         <f>B570-(1/1000)</f>
@@ -19373,18 +19369,18 @@
         <v>31</v>
       </c>
       <c r="E571" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F571" t="s">
         <v>14</v>
       </c>
       <c r="H571" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="572" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A572" t="s">
         <v>539</v>
-      </c>
-    </row>
-    <row r="572" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A572" t="s">
-        <v>540</v>
       </c>
       <c r="B572" s="4">
         <v>4.5799999999999999E-3</v>
@@ -19393,15 +19389,15 @@
         <v>13</v>
       </c>
       <c r="E572" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F572" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="573" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B573" s="4">
         <v>6.8599999999999998E-3</v>
@@ -19410,18 +19406,19 @@
         <v>13</v>
       </c>
       <c r="E573" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F573" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="575" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:21" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="575" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B575" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C575" s="10"/>
       <c r="K575" s="12"/>
@@ -19431,7 +19428,7 @@
       <c r="O575" s="12"/>
       <c r="P575" s="12"/>
     </row>
-    <row r="576" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" s="13" t="s">
         <v>3</v>
       </c>
@@ -19445,12 +19442,12 @@
       <c r="O576" s="12"/>
       <c r="P576" s="12"/>
     </row>
-    <row r="577" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B577" s="14" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K577" s="12"/>
       <c r="L577" s="12"/>
@@ -19459,7 +19456,7 @@
       <c r="O577" s="12"/>
       <c r="P577" s="12"/>
     </row>
-    <row r="578" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" s="13" t="s">
         <v>4</v>
       </c>
@@ -19473,7 +19470,7 @@
       <c r="O578" s="12"/>
       <c r="P578" s="12"/>
     </row>
-    <row r="579" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="13" t="s">
         <v>2</v>
       </c>
@@ -19487,7 +19484,7 @@
       <c r="O579" s="12"/>
       <c r="P579" s="12"/>
     </row>
-    <row r="580" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" s="13" t="s">
         <v>6</v>
       </c>
@@ -19504,7 +19501,7 @@
       <c r="O580" s="12"/>
       <c r="P580" s="12"/>
     </row>
-    <row r="581" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" s="17" t="s">
         <v>7</v>
       </c>
@@ -19524,7 +19521,7 @@
       <c r="O581" s="12"/>
       <c r="P581" s="12"/>
     </row>
-    <row r="582" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="17" t="s">
         <v>8</v>
       </c>
@@ -19589,7 +19586,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="583" spans="1:21" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:21" s="11" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" s="16" t="str">
         <f>B575</f>
         <v>deionized water production, via reverse osmosis, from sea water</v>
@@ -19625,7 +19622,7 @@
       <c r="P583" s="12"/>
       <c r="T583"/>
     </row>
-    <row r="584" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>33</v>
       </c>
@@ -19646,12 +19643,12 @@
         <v>36</v>
       </c>
       <c r="H584" t="s">
-        <v>533</v>
-      </c>
-      <c r="I584" s="60">
+        <v>532</v>
+      </c>
+      <c r="I584">
         <v>5</v>
       </c>
-      <c r="J584" s="61">
+      <c r="J584" s="4">
         <f>B584</f>
         <v>4.6500000000000005E-3</v>
       </c>
@@ -19664,7 +19661,7 @@
         <v>5.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="585" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>519</v>
       </c>
@@ -19683,11 +19680,11 @@
       <c r="G585" t="s">
         <v>520</v>
       </c>
-      <c r="I585" s="60">
+      <c r="I585">
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>521</v>
       </c>
@@ -19695,7 +19692,7 @@
         <v>7.5799999999999998E-7</v>
       </c>
       <c r="C586" s="11" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D586" t="s">
         <v>13</v>
@@ -19706,11 +19703,11 @@
       <c r="G586" t="s">
         <v>522</v>
       </c>
-      <c r="I586" s="60">
+      <c r="I586">
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:21" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>523</v>
       </c>
@@ -19729,13 +19726,13 @@
       <c r="G587" t="s">
         <v>524</v>
       </c>
-      <c r="I587" s="62">
+      <c r="I587">
         <v>0</v>
       </c>
     </row>
     <row r="588" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B588" s="4">
         <v>2.7E-6</v>
@@ -19750,15 +19747,15 @@
         <v>12</v>
       </c>
       <c r="G588" t="s">
-        <v>526</v>
-      </c>
-      <c r="I588" s="62">
+        <v>525</v>
+      </c>
+      <c r="I588">
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B589" s="4">
         <f>1/0.4/1000</f>
@@ -19768,18 +19765,18 @@
         <v>31</v>
       </c>
       <c r="E589" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F589" t="s">
         <v>14</v>
       </c>
       <c r="H589" t="s">
-        <v>536</v>
-      </c>
-      <c r="I589" s="62">
+        <v>535</v>
+      </c>
+      <c r="I589">
         <v>5</v>
       </c>
-      <c r="J589" s="61">
+      <c r="J589" s="4">
         <f>B589</f>
         <v>2.5000000000000001E-3</v>
       </c>
@@ -19792,8 +19789,22 @@
         <v>2.8571428571428571E-3</v>
       </c>
     </row>
+    <row r="590" spans="1:21" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="591" spans="1:21" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="592" spans="1:21" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="593" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="594" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="595" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="596" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="597" hidden="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:T597" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T597" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="market for acrylic dispersion, with water, in 58% solution state"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -19845,10 +19856,10 @@
       <c r="C4" s="38" t="s">
         <v>430</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="52" t="s">
         <v>395</v>
       </c>
-      <c r="E4" s="57"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="39" t="s">
         <v>396</v>
       </c>
@@ -19863,10 +19874,10 @@
       <c r="C5" s="38">
         <v>5.5</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="54">
         <v>2.5</v>
       </c>
-      <c r="E5" s="59"/>
+      <c r="E5" s="55"/>
       <c r="F5" s="38" t="s">
         <v>397</v>
       </c>
@@ -19878,9 +19889,9 @@
       <c r="B6" s="49" t="s">
         <v>399</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="40" t="s">
         <v>400</v>
       </c>
@@ -19895,10 +19906,10 @@
       <c r="C7" s="38">
         <v>20</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="54">
         <v>20</v>
       </c>
-      <c r="E7" s="59"/>
+      <c r="E7" s="55"/>
       <c r="F7" s="38" t="s">
         <v>396</v>
       </c>
@@ -19913,10 +19924,10 @@
       <c r="C8" s="38">
         <v>3</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="54">
         <v>7</v>
       </c>
-      <c r="E8" s="59"/>
+      <c r="E8" s="55"/>
       <c r="F8" s="38" t="s">
         <v>403</v>
       </c>
@@ -19928,9 +19939,9 @@
       <c r="B9" s="49" t="s">
         <v>431</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="40" t="s">
         <v>405</v>
       </c>
@@ -20002,7 +20013,7 @@
       <c r="D13" s="49">
         <v>23.6</v>
       </c>
-      <c r="E13" s="50"/>
+      <c r="E13" s="51"/>
       <c r="F13" s="38" t="s">
         <v>408</v>
       </c>
@@ -20015,8 +20026,8 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="C14" s="45"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="52"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="57"/>
       <c r="F14" s="40" t="s">
         <v>413</v>
       </c>
@@ -20034,7 +20045,7 @@
       <c r="D15" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="E15" s="50"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="38" t="s">
         <v>410</v>
       </c>
@@ -20052,7 +20063,7 @@
       <c r="D16" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="E16" s="50"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="38" t="s">
         <v>396</v>
       </c>
@@ -20067,27 +20078,27 @@
       <c r="C17" s="39" t="s">
         <v>424</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="58" t="s">
         <v>425</v>
       </c>
-      <c r="E17" s="54"/>
+      <c r="E17" s="59"/>
       <c r="F17" s="40" t="s">
         <v>426</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
